--- a/tame_output/ON/bt/strategyON_20240518.xlsx
+++ b/tame_output/ON/bt/strategyON_20240518.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>128.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-573.4%</t>
+          <t>-573.1%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-245.5%</t>
+          <t>-245.4%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-93.5%</t>
+          <t>-93.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781948</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567243</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76317867286043</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963421</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192819</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862988</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837685</v>
+        <v>3.821589933837683</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.272312868082736</v>
+        <v>-5.285745248365839</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.852136867708261</v>
+        <v>0.8467639155950195</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5438545251603539</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.15637301845755</v>
+        <v>-5.169805398740654</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8991913914756751</v>
+        <v>0.8938184393624335</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.46703279414423</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.913717430034387</v>
+        <v>-4.927149810317491</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9932516980649342</v>
+        <v>0.9878787459516922</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.46703279414423</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614594</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.693696631997376</v>
+        <v>-4.707129012280481</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.082839054290353</v>
+        <v>1.077466102177111</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.3258129490762498</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.560828942934099</v>
+        <v>-4.574261323217203</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.151880312717487</v>
+        <v>1.146507360604245</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.3258129490762498</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966262</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.401313839414729</v>
+        <v>-4.414746219697833</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.216832198565537</v>
+        <v>1.211459246452295</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1662978455568799</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046999</v>
+        <v>3.791269976046998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.256641694314991</v>
+        <v>-4.270074074598096</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.284789159166871</v>
+        <v>1.27941620705363</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.02162570045714246</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412108</v>
+        <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.316516521672684</v>
+        <v>-4.329948901955788</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24687671962522</v>
+        <v>1.241503767511979</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.08150052781483458</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144519</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.229717023893675</v>
+        <v>-4.24314940417678</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.30399701205939</v>
+        <v>1.298624059946148</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.08150052781483458</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900696</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.232186730355481</v>
+        <v>-4.245619110638586</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.303081530848079</v>
+        <v>1.297708578734838</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.08397023427664074</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473603</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.300556916679492</v>
+        <v>-4.313989296962596</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.286740378793177</v>
+        <v>1.281367426679936</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.0746945352404258</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978372</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.179140487053015</v>
+        <v>-4.19257286733612</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.325743659275659</v>
+        <v>1.320370707162418</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.0746945352404258</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710903155887704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.21013364638172</v>
+        <v>-4.223566026664825</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.138055960584564</v>
+        <v>1.132683008471322</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.0746945352404258</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675903</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.034659386589251</v>
+        <v>-4.048091766872355</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.21281289649334</v>
+        <v>1.207439944380098</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.0746945352404258</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.1455956392305</v>
+        <v>-4.159028019513604</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.144180424198047</v>
+        <v>1.138807472084805</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.0746945352404258</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.348622216773733</v>
+        <v>-4.362054597056837</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.066101178400659</v>
+        <v>1.060728226287418</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2777211127836592</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734164</v>
+        <v>3.784340376734162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.19069661783844</v>
+        <v>-4.204128998121544</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.139443804406909</v>
+        <v>1.134070852293667</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2777211127836592</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.104453154812062</v>
+        <v>-4.117885535095167</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.16888746019132</v>
+        <v>1.163514508078079</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2777211127836592</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786048</v>
+        <v>3.752023923786046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.105636239463124</v>
+        <v>-4.119068619746228</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.160190001775421</v>
+        <v>1.15481704966218</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2833641612501707</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273194</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.982508532469041</v>
+        <v>-3.995940912752145</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.209992957606156</v>
+        <v>1.204620005492914</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2833641612501707</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279503</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.889698051018181</v>
+        <v>-3.903130431301286</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.176389842077866</v>
+        <v>1.171016889964624</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1905536797993114</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030431</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.841134998797151</v>
+        <v>-3.854567379080255</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.197688538890878</v>
+        <v>1.192315586777637</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1419906275782812</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942743</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.728463780560901</v>
+        <v>-3.741896160844005</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.237832734697101</v>
+        <v>1.23245978258386</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.02931940934203098</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268541</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.616086779378228</v>
+        <v>-3.629519159661333</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.288274831000838</v>
+        <v>1.282901878887596</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.02931940934203098</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968866</v>
+        <v>3.689594264968864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.814321348264959</v>
+        <v>-3.827753728548063</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.220478205214685</v>
+        <v>1.215105253101443</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2275539782287616</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175326</v>
+        <v>3.643066046175324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.897322629290238</v>
+        <v>-3.910755009573342</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.025633412805226</v>
+        <v>1.020260460691985</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2461248627559353</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199273</v>
+        <v>3.682712735199271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.738128357233661</v>
+        <v>-3.751560737516766</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.209460782347062</v>
+        <v>1.204087830233821</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2461248627559353</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660772</v>
+        <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.824726940214764</v>
+        <v>-3.838159320497869</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.189334375256944</v>
+        <v>1.183961423143703</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2461248627559353</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383428</v>
+        <v>3.741170494383426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.786343277656613</v>
+        <v>-3.799775657939718</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.202107281622574</v>
+        <v>1.196734329509332</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2077412001977841</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002489</v>
+        <v>3.751143622002487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.609226947621447</v>
+        <v>-3.622659327904552</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.269682842481942</v>
+        <v>1.2643098903687</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2077412001977841</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263906</v>
+        <v>3.741324873263904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.579524823645154</v>
+        <v>-3.592957203928258</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.282247083834372</v>
+        <v>1.276874131721131</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2122113254130975</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072580148124</v>
+        <v>3.750725801481238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.400149402406385</v>
+        <v>-3.41358178268949</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.347784227636294</v>
+        <v>1.342411275523052</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.05543456724237883</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452235</v>
+        <v>3.716988143452233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.445163615926992</v>
+        <v>-3.458595996210096</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.310585997559641</v>
+        <v>1.305213045446399</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.08578346255698344</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979542</v>
+        <v>3.73702303297954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.712168126199427</v>
+        <v>-3.725600506482531</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.209475755789613</v>
+        <v>1.204102803676371</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.280146500599932</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230812</v>
+        <v>3.70230587923081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.000955346658342</v>
+        <v>-4.014387726941447</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.093164789502548</v>
+        <v>1.087791837389306</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3812326206989324</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285457</v>
+        <v>3.705568086285456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.96847976048757</v>
+        <v>-3.981912140770675</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.103754985525174</v>
+        <v>1.098382033411932</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3812326206989324</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848106</v>
+        <v>3.709506867848104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.949441632780273</v>
+        <v>-3.962874013063377</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.107894955816338</v>
+        <v>1.102522003703096</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4394162320301269</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601255</v>
+        <v>3.731060897601253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.966187498036648</v>
+        <v>-3.979619878319753</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.278778478652468</v>
+        <v>1.273405526539226</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4394162320301269</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537867</v>
+        <v>3.722443786537865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.01850787863744</v>
+        <v>-4.031940258920544</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.258683655398285</v>
+        <v>1.253310703285043</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4044693720212548</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259126</v>
+        <v>3.787422005259124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.162830784562359</v>
+        <v>-4.176263164845463</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.206963023425243</v>
+        <v>1.201590071312002</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4044693720212548</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989911</v>
+        <v>3.781497674989909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.015087814327356</v>
+        <v>-4.028520194610461</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.345212859311266</v>
+        <v>1.339839907198024</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2366620147863716</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.820221288622577</v>
+        <v>3.744608640334937</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.118144028636164</v>
+        <v>-4.115528665364448</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.306783995119224</v>
+        <v>1.30783014042791</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2366620147863716</v>

--- a/tame_output/ON/bt/strategyON_20240518.xlsx
+++ b/tame_output/ON/bt/strategyON_20240518.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>53.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>128.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-51.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-573.1%</t>
+          <t>-563.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-245.4%</t>
+          <t>-241.5%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>-93.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.76317867286043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837683</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.285745248365839</v>
+        <v>-5.272312868082736</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8467639155950195</v>
+        <v>0.852136867708261</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5438545251603539</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349965</v>
+        <v>3.822323422349967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.169805398740654</v>
+        <v>-5.15637301845755</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8938184393624335</v>
+        <v>0.8991913914756751</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.46703279414423</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972339</v>
+        <v>3.848613050972341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.927149810317491</v>
+        <v>-4.913717430034387</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9878787459516922</v>
+        <v>0.9932516980649342</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.46703279414423</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.81866537614594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.707129012280481</v>
+        <v>-4.693696631997376</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.077466102177111</v>
+        <v>1.082839054290353</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.3258129490762498</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.574261323217203</v>
+        <v>-4.560828942934099</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.146507360604245</v>
+        <v>1.151880312717487</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.3258129490762498</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.414746219697833</v>
+        <v>-4.401313839414729</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.211459246452295</v>
+        <v>1.216832198565537</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1662978455568799</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.270074074598096</v>
+        <v>-4.256641694314991</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.27941620705363</v>
+        <v>1.284789159166871</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.02162570045714246</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.329948901955788</v>
+        <v>-4.316516521672684</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.241503767511979</v>
+        <v>1.24687671962522</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.08150052781483458</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.24314940417678</v>
+        <v>-4.229717023893675</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.298624059946148</v>
+        <v>1.30399701205939</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.08150052781483458</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.245619110638586</v>
+        <v>-4.232186730355481</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.297708578734838</v>
+        <v>1.303081530848079</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.08397023427664074</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.313989296962596</v>
+        <v>-4.300556916679492</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.281367426679936</v>
+        <v>1.286740378793177</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.0746945352404258</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.19257286733612</v>
+        <v>-4.179140487053015</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.320370707162418</v>
+        <v>1.325743659275659</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.0746945352404258</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.223566026664825</v>
+        <v>-4.21013364638172</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.132683008471322</v>
+        <v>1.138055960584564</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.0746945352404258</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675902</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.048091766872355</v>
+        <v>-4.034659386589251</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.207439944380098</v>
+        <v>1.21281289649334</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.0746945352404258</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695447</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.159028019513604</v>
+        <v>-4.1455956392305</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.138807472084805</v>
+        <v>1.144180424198047</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.0746945352404258</v>
@@ -46194,10 +46194,10 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.362054597056837</v>
+        <v>-4.348622216773733</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.060728226287418</v>
+        <v>1.066101178400659</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2777211127836592</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.204128998121544</v>
+        <v>-4.19069661783844</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.134070852293667</v>
+        <v>1.139443804406909</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2777211127836592</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.117885535095167</v>
+        <v>-4.104453154812062</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.163514508078079</v>
+        <v>1.16888746019132</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2777211127836592</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.119068619746228</v>
+        <v>-4.105636239463124</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.15481704966218</v>
+        <v>1.160190001775421</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2833641612501707</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.995940912752145</v>
+        <v>-3.982508532469041</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.204620005492914</v>
+        <v>1.209992957606156</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2833641612501707</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.903130431301286</v>
+        <v>-3.889698051018181</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.171016889964624</v>
+        <v>1.176389842077866</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1905536797993114</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.854567379080255</v>
+        <v>-3.841134998797151</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.192315586777637</v>
+        <v>1.197688538890878</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1419906275782812</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.741896160844005</v>
+        <v>-3.728463780560901</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.23245978258386</v>
+        <v>1.237832734697101</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.02931940934203098</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.629519159661333</v>
+        <v>-3.616086779378228</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.282901878887596</v>
+        <v>1.288274831000838</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.02931940934203098</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.827753728548063</v>
+        <v>-3.814321348264959</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.215105253101443</v>
+        <v>1.220478205214685</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2275539782287616</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.910755009573342</v>
+        <v>-3.897322629290238</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.020260460691985</v>
+        <v>1.025633412805226</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2461248627559353</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.751560737516766</v>
+        <v>-3.738128357233661</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.204087830233821</v>
+        <v>1.209460782347062</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2461248627559353</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.838159320497869</v>
+        <v>-3.824726940214764</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.183961423143703</v>
+        <v>1.189334375256944</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2461248627559353</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.799775657939718</v>
+        <v>-3.786343277656613</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.196734329509332</v>
+        <v>1.202107281622574</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2077412001977841</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.622659327904552</v>
+        <v>-3.609226947621447</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.2643098903687</v>
+        <v>1.269682842481942</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2077412001977841</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.592957203928258</v>
+        <v>-3.579524823645154</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.276874131721131</v>
+        <v>1.282247083834372</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2122113254130975</v>
@@ -46562,10 +46562,10 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.41358178268949</v>
+        <v>-3.400149402406385</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.342411275523052</v>
+        <v>1.347784227636294</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.05543456724237883</v>
@@ -46585,10 +46585,10 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.458595996210096</v>
+        <v>-3.445163615926992</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.305213045446399</v>
+        <v>1.310585997559641</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.08578346255698344</v>
@@ -46608,10 +46608,10 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.725600506482531</v>
+        <v>-3.712168126199427</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.204102803676371</v>
+        <v>1.209475755789613</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.280146500599932</v>
@@ -46631,10 +46631,10 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.014387726941447</v>
+        <v>-4.000955346658342</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.087791837389306</v>
+        <v>1.093164789502548</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3812326206989324</v>
@@ -46654,10 +46654,10 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.981912140770675</v>
+        <v>-3.96847976048757</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.098382033411932</v>
+        <v>1.103754985525174</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3812326206989324</v>
@@ -46677,10 +46677,10 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.962874013063377</v>
+        <v>-3.949441632780273</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.102522003703096</v>
+        <v>1.107894955816338</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4394162320301269</v>
@@ -46700,10 +46700,10 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.979619878319753</v>
+        <v>-3.966187498036648</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.273405526539226</v>
+        <v>1.278778478652468</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4394162320301269</v>
@@ -46723,10 +46723,10 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.031940258920544</v>
+        <v>-4.01850787863744</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.253310703285043</v>
+        <v>1.258683655398285</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4044693720212548</v>
@@ -46746,10 +46746,10 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.176263164845463</v>
+        <v>-4.162830784562359</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.201590071312002</v>
+        <v>1.206963023425243</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4044693720212548</v>
@@ -46769,10 +46769,10 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.028520194610461</v>
+        <v>-4.015087814327356</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.339839907198024</v>
+        <v>1.345212859311266</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2366620147863716</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.744608640334937</v>
+        <v>3.820221288622575</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.115528665364448</v>
+        <v>-4.01704811730295</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.30783014042791</v>
+        <v>1.34722235965251</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2366620147863716</v>

--- a/tame_output/ON/bt/strategyON_20240518.xlsx
+++ b/tame_output/ON/bt/strategyON_20240518.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>110.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.1%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-72.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-563.3%</t>
+          <t>-574.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-241.5%</t>
+          <t>-246.0%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-20.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-93.5%</t>
+          <t>-93.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76317867286043</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963421</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192819</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862988</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821589933837683</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.272312868082736</v>
+        <v>-5.285745248365839</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.852136867708261</v>
+        <v>0.8467639155950195</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5438545251603539</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349967</v>
+        <v>3.822323422349965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.15637301845755</v>
+        <v>-5.169805398740654</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8991913914756751</v>
+        <v>0.8938184393624335</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.46703279414423</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972341</v>
+        <v>3.848613050972339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.913717430034387</v>
+        <v>-4.927149810317491</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9932516980649342</v>
+        <v>0.9878787459516922</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.46703279414423</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614594</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.693696631997376</v>
+        <v>-4.707129012280481</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.082839054290353</v>
+        <v>1.077466102177111</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.3258129490762498</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.560828942934099</v>
+        <v>-4.574261323217203</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.151880312717487</v>
+        <v>1.146507360604245</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.3258129490762498</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.401313839414729</v>
+        <v>-4.414746219697833</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.216832198565537</v>
+        <v>1.211459246452295</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1662978455568799</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.256641694314991</v>
+        <v>-4.270074074598096</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.284789159166871</v>
+        <v>1.27941620705363</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.02162570045714246</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.316516521672684</v>
+        <v>-4.329948901955788</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.24687671962522</v>
+        <v>1.241503767511979</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.08150052781483458</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.229717023893675</v>
+        <v>-4.24314940417678</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.30399701205939</v>
+        <v>1.298624059946148</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.08150052781483458</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.232186730355481</v>
+        <v>-4.245619110638586</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.303081530848079</v>
+        <v>1.297708578734838</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.08397023427664074</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.300556916679492</v>
+        <v>-4.313989296962596</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.286740378793177</v>
+        <v>1.281367426679936</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.0746945352404258</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.179140487053015</v>
+        <v>-4.19257286733612</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.325743659275659</v>
+        <v>1.320370707162418</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.0746945352404258</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.21013364638172</v>
+        <v>-4.223566026664825</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.138055960584564</v>
+        <v>1.132683008471322</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.0746945352404258</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675902</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.034659386589251</v>
+        <v>-4.048091766872355</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.21281289649334</v>
+        <v>1.207439944380098</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.0746945352404258</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.1455956392305</v>
+        <v>-4.159028019513604</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.144180424198047</v>
+        <v>1.138807472084805</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.0746945352404258</v>
@@ -46194,10 +46194,10 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.348622216773733</v>
+        <v>-4.362054597056837</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.066101178400659</v>
+        <v>1.060728226287418</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2777211127836592</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.19069661783844</v>
+        <v>-4.204128998121544</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.139443804406909</v>
+        <v>1.134070852293667</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2777211127836592</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.104453154812062</v>
+        <v>-4.117885535095167</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.16888746019132</v>
+        <v>1.163514508078079</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2777211127836592</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.105636239463124</v>
+        <v>-4.119068619746228</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.160190001775421</v>
+        <v>1.15481704966218</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2833641612501707</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.982508532469041</v>
+        <v>-3.995940912752145</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.209992957606156</v>
+        <v>1.204620005492914</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2833641612501707</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.889698051018181</v>
+        <v>-3.903130431301286</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.176389842077866</v>
+        <v>1.171016889964624</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1905536797993114</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.841134998797151</v>
+        <v>-3.854567379080255</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.197688538890878</v>
+        <v>1.192315586777637</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1419906275782812</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.728463780560901</v>
+        <v>-3.741896160844005</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.237832734697101</v>
+        <v>1.23245978258386</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.02931940934203098</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.616086779378228</v>
+        <v>-3.629519159661333</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.288274831000838</v>
+        <v>1.282901878887596</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.02931940934203098</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.814321348264959</v>
+        <v>-3.827753728548063</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.220478205214685</v>
+        <v>1.215105253101443</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2275539782287616</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.897322629290238</v>
+        <v>-3.910755009573342</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.025633412805226</v>
+        <v>1.020260460691985</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2461248627559353</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.738128357233661</v>
+        <v>-3.751560737516766</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.209460782347062</v>
+        <v>1.204087830233821</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2461248627559353</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.824726940214764</v>
+        <v>-3.838159320497869</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.189334375256944</v>
+        <v>1.183961423143703</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2461248627559353</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.786343277656613</v>
+        <v>-3.799775657939718</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.202107281622574</v>
+        <v>1.196734329509332</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2077412001977841</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.609226947621447</v>
+        <v>-3.622659327904552</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.269682842481942</v>
+        <v>1.2643098903687</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2077412001977841</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.579524823645154</v>
+        <v>-3.592957203928258</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.282247083834372</v>
+        <v>1.276874131721131</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2122113254130975</v>
@@ -46562,10 +46562,10 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.400149402406385</v>
+        <v>-3.41358178268949</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.347784227636294</v>
+        <v>1.342411275523052</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.05543456724237883</v>
@@ -46585,10 +46585,10 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.445163615926992</v>
+        <v>-3.458595996210096</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.310585997559641</v>
+        <v>1.305213045446399</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.08578346255698344</v>
@@ -46608,10 +46608,10 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.712168126199427</v>
+        <v>-3.725600506482531</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.209475755789613</v>
+        <v>1.204102803676371</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.280146500599932</v>
@@ -46631,10 +46631,10 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.000955346658342</v>
+        <v>-4.014387726941447</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.093164789502548</v>
+        <v>1.087791837389306</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3812326206989324</v>
@@ -46654,10 +46654,10 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.96847976048757</v>
+        <v>-3.981912140770675</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.103754985525174</v>
+        <v>1.098382033411932</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3812326206989324</v>
@@ -46677,10 +46677,10 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.949441632780273</v>
+        <v>-3.962874013063377</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.107894955816338</v>
+        <v>1.102522003703096</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4394162320301269</v>
@@ -46700,10 +46700,10 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.966187498036648</v>
+        <v>-3.979619878319753</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.278778478652468</v>
+        <v>1.273405526539226</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4394162320301269</v>
@@ -46723,10 +46723,10 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.01850787863744</v>
+        <v>-4.031940258920544</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.258683655398285</v>
+        <v>1.253310703285043</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4044693720212548</v>
@@ -46746,10 +46746,10 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.162830784562359</v>
+        <v>-4.176263164845463</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.206963023425243</v>
+        <v>1.201590071312002</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4044693720212548</v>
@@ -46769,10 +46769,10 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.015087814327356</v>
+        <v>-4.028520194610461</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.345212859311266</v>
+        <v>1.339839907198024</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2366620147863716</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.820221288622575</v>
+        <v>3.744608640334937</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.01704811730295</v>
+        <v>-4.130534877141682</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.34722235965251</v>
+        <v>1.301827655717017</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2366620147863716</v>

--- a/tame_output/ON/bt/strategyON_20240518.xlsx
+++ b/tame_output/ON/bt/strategyON_20240518.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-17.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>128.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-51.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.6%</t>
+          <t>-564.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-246.0%</t>
+          <t>-241.9%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-164.8%</t>
+          <t>-152.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1967"/>
+  <dimension ref="A1:G1968"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837683</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.285745248365839</v>
+        <v>-5.283171857502104</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8467639155950195</v>
+        <v>0.8477932719405135</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5438545251603539</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349965</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.169805398740654</v>
+        <v>-5.167232007876919</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8938184393624335</v>
+        <v>0.8948477957079279</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.46703279414423</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972339</v>
+        <v>3.848613050972338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.927149810317491</v>
+        <v>-4.924576419453755</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9878787459516922</v>
+        <v>0.9889081022971866</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.46703279414423</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.707129012280481</v>
+        <v>-4.704555621416745</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.077466102177111</v>
+        <v>1.078495458522605</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.3258129490762498</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.574261323217203</v>
+        <v>-4.571687932353467</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.146507360604245</v>
+        <v>1.147536716949739</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.3258129490762498</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.414746219697833</v>
+        <v>-4.412172828834097</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.211459246452295</v>
+        <v>1.212488602797789</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1662978455568799</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046998</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.270074074598096</v>
+        <v>-4.26750068373436</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.27941620705363</v>
+        <v>1.280445563399124</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.02162570045714246</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412106</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.329948901955788</v>
+        <v>-4.327375511092052</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.241503767511979</v>
+        <v>1.242533123857473</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.08150052781483458</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.24314940417678</v>
+        <v>-4.240576013313044</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.298624059946148</v>
+        <v>1.299653416291642</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.08150052781483458</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.245619110638586</v>
+        <v>-4.24304571977485</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.297708578734838</v>
+        <v>1.298737935080332</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.08397023427664074</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.313989296962596</v>
+        <v>-4.31141590609886</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.281367426679936</v>
+        <v>1.28239678302543</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.0746945352404258</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.19257286733612</v>
+        <v>-4.189999476472384</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.320370707162418</v>
+        <v>1.321400063507912</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.0746945352404258</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887704</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.223566026664825</v>
+        <v>-4.220992635801089</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.132683008471322</v>
+        <v>1.133712364816817</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.0746945352404258</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.048091766872355</v>
+        <v>-4.045518376008619</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.207439944380098</v>
+        <v>1.208469300725592</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.0746945352404258</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695447</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.159028019513604</v>
+        <v>-4.156454628649868</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.138807472084805</v>
+        <v>1.1398368284303</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.0746945352404258</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.362054597056837</v>
+        <v>-4.359481206193101</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.060728226287418</v>
+        <v>1.061757582632912</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2777211127836592</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734162</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.204128998121544</v>
+        <v>-4.201555607257808</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.134070852293667</v>
+        <v>1.135100208639162</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2777211127836592</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212299</v>
+        <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.117885535095167</v>
+        <v>-4.115312144231431</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.163514508078079</v>
+        <v>1.164543864423573</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2777211127836592</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786046</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.119068619746228</v>
+        <v>-4.116495228882492</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.15481704966218</v>
+        <v>1.155846406007674</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2833641612501707</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.995940912752145</v>
+        <v>-3.993367521888409</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.204620005492914</v>
+        <v>1.205649361838409</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2833641612501707</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.903130431301286</v>
+        <v>-3.90055704043755</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.171016889964624</v>
+        <v>1.172046246310118</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1905536797993114</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.854567379080255</v>
+        <v>-3.85199398821652</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.192315586777637</v>
+        <v>1.193344943123131</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1419906275782812</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.741896160844005</v>
+        <v>-3.739322769980269</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.23245978258386</v>
+        <v>1.233489138929354</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.02931940934203098</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.629519159661333</v>
+        <v>-3.626945768797597</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.282901878887596</v>
+        <v>1.28393123523309</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.02931940934203098</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968864</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.827753728548063</v>
+        <v>-3.825180337684327</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.215105253101443</v>
+        <v>1.216134609446937</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2275539782287616</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175324</v>
+        <v>3.643066046175322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.910755009573342</v>
+        <v>-3.908181618709606</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.020260460691985</v>
+        <v>1.021289817037479</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2461248627559353</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199271</v>
+        <v>3.682712735199269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.751560737516766</v>
+        <v>-3.74898734665303</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.204087830233821</v>
+        <v>1.205117186579315</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2461248627559353</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660771</v>
+        <v>3.733008865660769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.838159320497869</v>
+        <v>-3.835585929634133</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.183961423143703</v>
+        <v>1.184990779489197</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2461248627559353</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383426</v>
+        <v>3.741170494383424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.799775657939718</v>
+        <v>-3.797202267075982</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.196734329509332</v>
+        <v>1.197763685854826</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2077412001977841</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002487</v>
+        <v>3.751143622002485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.622659327904552</v>
+        <v>-3.620085937040816</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.2643098903687</v>
+        <v>1.265339246714194</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2077412001977841</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263904</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.592957203928258</v>
+        <v>-3.590383813064522</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.276874131721131</v>
+        <v>1.277903488066625</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2122113254130975</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481238</v>
+        <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.41358178268949</v>
+        <v>-3.411008391825754</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.342411275523052</v>
+        <v>1.343440631868547</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.05543456724237883</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452233</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.458595996210096</v>
+        <v>-3.45602260534636</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.305213045446399</v>
+        <v>1.306242401791894</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.08578346255698344</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702303297954</v>
+        <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.725600506482531</v>
+        <v>-3.723027115618796</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.204102803676371</v>
+        <v>1.205132160021865</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.280146500599932</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230587923081</v>
+        <v>3.702305879230808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.014387726941447</v>
+        <v>-4.011814336077711</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.087791837389306</v>
+        <v>1.088821193734801</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3812326206989324</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285456</v>
+        <v>3.705568086285454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.981912140770675</v>
+        <v>-3.979338749906939</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.098382033411932</v>
+        <v>1.099411389757426</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3812326206989324</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848104</v>
+        <v>3.709506867848102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.962874013063377</v>
+        <v>-3.960300622199641</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.102522003703096</v>
+        <v>1.10355136004859</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.4394162320301269</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601253</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.979619878319753</v>
+        <v>-3.977046487456017</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.273405526539226</v>
+        <v>1.274434882884721</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.4394162320301269</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537865</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.031940258920544</v>
+        <v>-4.029366868056808</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.253310703285043</v>
+        <v>1.254340059630537</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4044693720212548</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259124</v>
+        <v>3.787422005259122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.176263164845463</v>
+        <v>-4.173689773981727</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.201590071312002</v>
+        <v>1.202619427657496</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4044693720212548</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989909</v>
+        <v>3.781497674989907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.028520194610461</v>
+        <v>-4.025946803746725</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.339839907198024</v>
+        <v>1.340869263543519</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2366620147863716</v>
@@ -46786,22 +46786,45 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.744608640334937</v>
+        <v>3.80224235365117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.130534877141682</v>
+        <v>-4.027907106722318</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.301827655717017</v>
+        <v>1.342878763884762</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2366620147863716</v>
       </c>
       <c r="G1967" t="n">
         <v>2.812400822015614</v>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" s="2" t="n">
+        <v>45430</v>
+      </c>
+      <c r="B1968" t="n">
+        <v>3.745779935064943</v>
+      </c>
+      <c r="C1968" t="n">
+        <v>2.942820120104948</v>
+      </c>
+      <c r="D1968" t="n">
+        <v>-4.027907106722318</v>
+      </c>
+      <c r="E1968" t="n">
+        <v>1.342878763884762</v>
+      </c>
+      <c r="F1968" t="n">
+        <v>-0.2366620147863716</v>
+      </c>
+      <c r="G1968" t="n">
+        <v>2.935883917091316</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240518.xlsx
+++ b/tame_output/ON/bt/strategyON_20240518.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.1%</t>
+          <t>127.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-52.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.8%</t>
+          <t>448.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-564.4%</t>
+          <t>-583.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-40.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-241.9%</t>
+          <t>-249.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-31.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-93.6%</t>
+          <t>-92.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.7%</t>
+          <t>-266.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-152.4%</t>
+          <t>-135.7%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.580842483270056</v>
+        <v>-7.468205126665516</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.08618527607091897</v>
+        <v>0.1312402187127351</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.926717305254865</v>
+        <v>-7.814079948650324</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05606508757730966</v>
+        <v>-0.01101014493549313</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.090297183439249</v>
+        <v>-7.977659826834708</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1230921187960621</v>
+        <v>-0.07803717615424599</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.386958525249447</v>
+        <v>-8.274321168644907</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2379776795909332</v>
+        <v>-0.1929227369491171</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.510202914464877</v>
+        <v>-8.397565557860336</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2913017398115083</v>
+        <v>-0.2462467971696918</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.893204303207508</v>
+        <v>-8.780566946602967</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4446043966301447</v>
+        <v>-0.3995494539883282</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.050603183420629</v>
+        <v>-8.937965826816088</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.504992432743963</v>
+        <v>-0.4599374901021465</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.41013350592463</v>
+        <v>-9.297496149320089</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6434542584475134</v>
+        <v>-0.5983993158056968</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.460482569378852</v>
+        <v>-9.347845212774311</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6556778638720249</v>
+        <v>-0.6106229212302083</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.67963153745305</v>
+        <v>-9.566994180848509</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7402957004799346</v>
+        <v>-0.6952407578381186</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.984577007876364</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.675940612496639</v>
+        <v>-9.563303255892098</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7388193304973707</v>
+        <v>-0.6937643878555542</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.984577007876364</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.880198787826503</v>
+        <v>-9.767561431221962</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8150094035106736</v>
+        <v>-0.7699544608688571</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.112215952490353</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.09823655945768</v>
+        <v>-9.985599202853139</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8977419576787082</v>
+        <v>-0.8526870150368921</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.286986720586252</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.02476672779023</v>
+        <v>-9.91212937118569</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.852982323518308</v>
+        <v>-0.8079273808764915</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.213516888918803</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.19989114517677</v>
+        <v>-10.08725378857223</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9084768697254084</v>
+        <v>-0.8634219270835919</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.388641306305347</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.43434323919126</v>
+        <v>-10.32170588258672</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.0094768722328</v>
+        <v>-0.9644219295909839</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.388641306305347</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.7221470837285</v>
+        <v>-10.60950972712396</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.131270600821672</v>
+        <v>-1.086215658179855</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.676445150842585</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.77493323932883</v>
+        <v>-10.66229588272429</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.151269273223246</v>
+        <v>-1.10621433058143</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.772120637424982</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.00696215906509</v>
+        <v>-10.89432480246055</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.241387112488636</v>
+        <v>-1.19633216984682</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.834133334613405</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.95494664509628</v>
+        <v>-10.84230928849174</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.21659057121471</v>
+        <v>-1.171535628572894</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.834133334613405</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.0966184868204</v>
+        <v>-10.98398113021586</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.2747345348031</v>
+        <v>-1.229679592161284</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.834133334613405</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.04702764239556</v>
+        <v>-10.93439028579102</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.239844786868294</v>
+        <v>-1.194789844226478</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.784542490188572</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.84787553515847</v>
+        <v>-10.73523817855392</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.173235077620137</v>
+        <v>-1.128180134978321</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.619219964238758</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.62203038243905</v>
+        <v>-10.50939302583451</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.073317943496164</v>
+        <v>-1.028263000854348</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.577293288651595</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.49745172610146</v>
+        <v>-10.38481436949692</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.022347336405069</v>
+        <v>-0.9772923937632521</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.577293288651595</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.55034701414575</v>
+        <v>-10.43770965754121</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.040871677460675</v>
+        <v>-0.9958167348188587</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.572337942563149</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.266438283217</v>
+        <v>-10.15380092661246</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9215744808505395</v>
+        <v>-0.876519538208723</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.572337942563149</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.19507189060735</v>
+        <v>-10.08243453400281</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9027651862005452</v>
+        <v>-0.8577102435587296</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.500971549953501</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.931235023403282</v>
+        <v>-9.818597666798741</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8071139206318252</v>
+        <v>-0.7620589779900091</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.500971549953501</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.663993222534884</v>
+        <v>-9.551355865930343</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7020517607838399</v>
+        <v>-0.6569968181420234</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.500971549953501</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.566086183858394</v>
+        <v>-9.453448827253853</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6631892602867047</v>
+        <v>-0.6181343176448881</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.432985800092944</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.542132642882436</v>
+        <v>-9.429495286277895</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6529393377508277</v>
+        <v>-0.6078843951090112</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.409032259116987</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.278072704559639</v>
+        <v>-9.165435347955098</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.560575678583461</v>
+        <v>-0.5155207359416449</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.144972320794191</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309725</v>
+        <v>3.833249172309723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.570993081054802</v>
+        <v>-8.458355724450261</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.280530862841827</v>
+        <v>-0.2354759202000105</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.144972320794191</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.839370871858726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.530808782688611</v>
+        <v>-8.41817142608407</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2641135196075095</v>
+        <v>-0.219058576965693</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.104788022428</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.450738987150807</v>
+        <v>-8.338101630546266</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2327187801716306</v>
+        <v>-0.1876638375298145</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.024718226890196</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.217257764921207</v>
+        <v>-8.104620408316666</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1314018624419386</v>
+        <v>-0.0863469198001221</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.791237004660597</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.067591373913693</v>
+        <v>-7.954954017309151</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.07442751635189193</v>
+        <v>-0.0293725737100754</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.698333513418061</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.935315900282807</v>
+        <v>-7.822678543678265</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.02614984015251043</v>
+        <v>0.0189051024893061</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.566058039787175</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.744716225609654</v>
+        <v>-7.632078869005112</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.05290509040438707</v>
+        <v>0.09796003304620404</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.375458365114022</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.495716426926073</v>
+        <v>-7.383079070321531</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1654113511014783</v>
+        <v>0.2104662937432953</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.375458365114022</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.601306416699178</v>
+        <v>-7.488669060094636</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.004800574406981895</v>
+        <v>0.04025436823483464</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.481048354887126</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.620041318817774</v>
+        <v>-7.507403962213233</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.0362498066226653</v>
+        <v>0.08130474926448228</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.481048354887126</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.472101277410175</v>
+        <v>-7.359463920805633</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.02445309950246255</v>
+        <v>0.02060184313935443</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.460727438978569</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.7235626538792</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.447872641021203</v>
+        <v>-7.335235284416661</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.02347563120035145</v>
+        <v>0.02157931144146508</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.436498802589596</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.404324234250512</v>
+        <v>-7.29168687764597</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.01301688058716843</v>
+        <v>0.0320380620546481</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.436498802589596</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.162175840796654</v>
+        <v>-7.049538484192112</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.09830483117551791</v>
+        <v>0.1433597738173344</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.436498802589596</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.098946469028306</v>
+        <v>-6.986309112423764</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1181287003420524</v>
+        <v>0.1631836429838689</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.436498802589596</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.975655334211175</v>
+        <v>-6.863017977606633</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1649432482794815</v>
+        <v>0.209998190921298</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.313207667772466</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.954506135307732</v>
+        <v>-6.84186877870319</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1811039060781838</v>
+        <v>0.2261588487200008</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.292058468869023</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.710740693324287</v>
+        <v>-6.598103336719745</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2743907912186123</v>
+        <v>0.3194457338604288</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.292058468869023</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.563843665606417</v>
+        <v>-6.451206309001876</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3352739162257765</v>
+        <v>0.380328858867593</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.244400226890435</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.313993271657342</v>
+        <v>-6.201355915052801</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4279561487891086</v>
+        <v>0.4730110914309251</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.244400226890435</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.13810117918991</v>
+        <v>-6.025463822585369</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5019121092967302</v>
+        <v>0.5469670519385463</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.244400226890435</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.966654716167446</v>
+        <v>-5.854017359562905</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5838182005602692</v>
+        <v>0.6288731432020858</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.072953763867972</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.741621716498623</v>
+        <v>-5.628984359894083</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6728518780440953</v>
+        <v>0.7179068206859118</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8479207641991487</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.677985974264689</v>
+        <v>-5.565348617660148</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7030009759919866</v>
+        <v>0.7480559186338027</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7842850219652142</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.584985933058791</v>
+        <v>-5.47234857645425</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7213952512581416</v>
+        <v>0.7664501938999577</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7842850219652142</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712292</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.34455543625393</v>
+        <v>-5.23191807964939</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.819310526604963</v>
+        <v>0.8643654692467795</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5438545251603539</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.283171857502104</v>
+        <v>-5.159675511478195</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8477932719405135</v>
+        <v>0.8971918103500776</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5438545251603539</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.167232007876919</v>
+        <v>-5.04373566185301</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8948477957079279</v>
+        <v>0.9442463341174916</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.46703279414423</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972338</v>
+        <v>3.848613050972336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.924576419453755</v>
+        <v>-4.801080073429846</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9889081022971866</v>
+        <v>1.03830664070675</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.46703279414423</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145938</v>
+        <v>3.818665376145936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.704555621416745</v>
+        <v>-4.581059275392835</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.078495458522605</v>
+        <v>1.127893996932169</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.3258129490762498</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.571687932353467</v>
+        <v>-4.448191586329558</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.147536716949739</v>
+        <v>1.196935255359303</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.3258129490762498</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.412172828834097</v>
+        <v>-4.288676482810188</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.212488602797789</v>
+        <v>1.261887141207353</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1662978455568799</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.26750068373436</v>
+        <v>-4.144004337710451</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.280445563399124</v>
+        <v>1.329844101808688</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.02162570045714246</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.327375511092052</v>
+        <v>-4.203879165068143</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.242533123857473</v>
+        <v>1.291931662267037</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.08150052781483458</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.240576013313044</v>
+        <v>-4.117079667289135</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.299653416291642</v>
+        <v>1.349051954701206</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.08150052781483458</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.24304571977485</v>
+        <v>-4.119549373750941</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.298737935080332</v>
+        <v>1.348136473489896</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.08397023427664074</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.31141590609886</v>
+        <v>-4.187919560074951</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.28239678302543</v>
+        <v>1.331795321434994</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.0746945352404258</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.189999476472384</v>
+        <v>-4.066503130448474</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.321400063507912</v>
+        <v>1.370798601917476</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.0746945352404258</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.7109031558877</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.220992635801089</v>
+        <v>-4.09749628977718</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.133712364816817</v>
+        <v>1.18311090322638</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.0746945352404258</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.045518376008619</v>
+        <v>-3.92202202998471</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.208469300725592</v>
+        <v>1.257867839135156</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.0746945352404258</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.156454628649868</v>
+        <v>-4.032958282625959</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.1398368284303</v>
+        <v>1.189235366839863</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.0746945352404258</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581292</v>
+        <v>3.773206721581288</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.359481206193101</v>
+        <v>-4.235984860169192</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.061757582632912</v>
+        <v>1.111156121042476</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2777211127836592</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734157</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.201555607257808</v>
+        <v>-4.078059261233899</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.135100208639162</v>
+        <v>1.184498747048725</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2777211127836592</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>3.786946382212293</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.115312144231431</v>
+        <v>-3.991815798207521</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.164543864423573</v>
+        <v>1.213942402833137</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2777211127836592</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786041</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.116495228882492</v>
+        <v>-3.992998882858582</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.155846406007674</v>
+        <v>1.205244944417238</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2833641612501707</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.993367521888409</v>
+        <v>-3.869871175864499</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.205649361838409</v>
+        <v>1.255047900247973</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2833641612501707</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.90055704043755</v>
+        <v>-3.77706069441364</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.172046246310118</v>
+        <v>1.221444784719682</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1905536797993114</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.85199398821652</v>
+        <v>-3.728497642192609</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.193344943123131</v>
+        <v>1.242743481532695</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1419906275782812</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.739322769980269</v>
+        <v>-3.615826423956359</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.233489138929354</v>
+        <v>1.282887677338918</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.02931940934203098</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.626945768797597</v>
+        <v>-3.503449422773687</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.28393123523309</v>
+        <v>1.333329773642654</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.02931940934203098</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.689594264968859</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.825180337684327</v>
+        <v>-3.701683991660417</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.216134609446937</v>
+        <v>1.265533147856501</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2275539782287616</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175322</v>
+        <v>3.643066046175319</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.908181618709606</v>
+        <v>-3.784685272685696</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.021289817037479</v>
+        <v>1.070688355447043</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2461248627559353</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199269</v>
+        <v>3.682712735199266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.74898734665303</v>
+        <v>-3.62549100062912</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.205117186579315</v>
+        <v>1.254515724988879</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2461248627559353</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660769</v>
+        <v>3.733008865660765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.835585929634133</v>
+        <v>-3.712089583610223</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.184990779489197</v>
+        <v>1.234389317898761</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2461248627559353</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383424</v>
+        <v>3.741170494383421</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.797202267075982</v>
+        <v>-3.673705921052071</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.197763685854826</v>
+        <v>1.24716222426439</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2077412001977841</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002485</v>
+        <v>3.751143622002481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.620085937040816</v>
+        <v>-3.496589591016905</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.265339246714194</v>
+        <v>1.314737785123758</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2077412001977841</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.741324873263899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.590383813064522</v>
+        <v>-3.466887467040612</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.277903488066625</v>
+        <v>1.327302026476189</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2122113254130975</v>
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481235</v>
+        <v>3.750725801481232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.411008391825754</v>
+        <v>-3.497901787404992</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.343440631868547</v>
+        <v>1.308683273636851</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.05543456724237883</v>
+        <v>-0.2480455753649109</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.674939672567168</v>
+        <v>2.559373067693649</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.45602260534636</v>
+        <v>-3.542916000925598</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.306242401791894</v>
+        <v>1.271485043560199</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.08578346255698344</v>
+        <v>-0.2783944706795155</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.637537790709995</v>
+        <v>2.521971185836476</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979537</v>
+        <v>3.737023032979534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.723027115618796</v>
+        <v>-3.809920511198033</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.205132160021865</v>
+        <v>1.17037480179017</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.280146500599932</v>
+        <v>-0.4727575087224641</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.526611530223172</v>
+        <v>2.411044925349653</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230808</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.011814336077711</v>
+        <v>-4.098707731656948</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.088821193734801</v>
+        <v>1.054063835503106</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.5738436288214644</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.465163780060273</v>
+        <v>2.349597175186754</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285454</v>
+        <v>3.705568086285451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.979338749906939</v>
+        <v>-4.066232145486176</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.099411389757426</v>
+        <v>1.064654031525731</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.5738436288214644</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.46276374161459</v>
+        <v>2.34719713674107</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848102</v>
+        <v>3.709506867848099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.960300622199641</v>
+        <v>-4.047194017778879</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.10355136004859</v>
+        <v>1.068794001816895</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.632027240152659</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.424378294024118</v>
+        <v>2.308811689150599</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.73106089760125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.977046487456017</v>
+        <v>-4.063939883035254</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.274434882884721</v>
+        <v>1.239677524653026</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.632027240152659</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.601960162962799</v>
+        <v>2.486393558089279</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.029366868056808</v>
+        <v>-4.116260263636046</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.254340059630537</v>
+        <v>1.219582701398843</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.5970803801437868</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.623761607954255</v>
+        <v>2.508195003080736</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259122</v>
+        <v>3.787422005259121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.173689773981727</v>
+        <v>-4.260583169560965</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.202619427657496</v>
+        <v>1.167862069425801</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.5970803801437868</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.629770138351181</v>
+        <v>2.514203533477662</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989907</v>
+        <v>3.781497674989906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.025946803746725</v>
+        <v>-4.112840199325962</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.340869263543519</v>
+        <v>1.306111905311824</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.4292730229089037</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.809607200484133</v>
+        <v>2.694040595610614</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224235365117</v>
+        <v>3.802242353651168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.027907106722318</v>
+        <v>-4.214854881857184</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.342878763884762</v>
+        <v>1.268099653830816</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.4292730229089037</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.812400822015614</v>
+        <v>2.696834217142095</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.745779935064943</v>
+        <v>3.822680306802603</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.942820120104948</v>
+        <v>3.109708608571037</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.027907106722318</v>
+        <v>-4.214854881857184</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.342878763884762</v>
+        <v>1.268099653830816</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.4292730229089037</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.935883917091316</v>
+        <v>3.102772405557405</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240518.xlsx
+++ b/tame_output/ON/bt/strategyON_20240518.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.1%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.0%</t>
+          <t>-51.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.3%</t>
+          <t>448.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.1%</t>
+          <t>-562.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-249.4%</t>
+          <t>-241.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.8%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-92.4%</t>
+          <t>-93.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-266.9%</t>
+          <t>-247.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.468205126665516</v>
+        <v>-7.472502113040866</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1312402187127351</v>
+        <v>0.1295214241625948</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.814079948650324</v>
+        <v>-7.818376935025675</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.01101014493549313</v>
+        <v>-0.01272893948563381</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.977659826834708</v>
+        <v>-7.98195681321006</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.07803717615424599</v>
+        <v>-0.07975597070438623</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.274321168644907</v>
+        <v>-8.278618155020258</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1929227369491171</v>
+        <v>-0.1946415314992573</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.397565557860336</v>
+        <v>-8.401862544235687</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2462467971696918</v>
+        <v>-0.2479655917198325</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.780566946602967</v>
+        <v>-8.784863932978318</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.3995494539883282</v>
+        <v>-0.4012682485384689</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.937965826816088</v>
+        <v>-8.942262813191439</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4599374901021465</v>
+        <v>-0.4616562846522871</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.297496149320089</v>
+        <v>-9.301793135695441</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.5983993158056968</v>
+        <v>-0.6001181103558375</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.347845212774311</v>
+        <v>-9.352142199149663</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6106229212302083</v>
+        <v>-0.612341715780349</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.566994180848509</v>
+        <v>-9.57129116722386</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6952407578381186</v>
+        <v>-0.6969595523882588</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.984577007876364</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.563303255892098</v>
+        <v>-9.567600242267449</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6937643878555542</v>
+        <v>-0.6954831824056948</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.984577007876364</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.767561431221962</v>
+        <v>-9.771858417597313</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7699544608688571</v>
+        <v>-0.7716732554189978</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.112215952490353</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.985599202853139</v>
+        <v>-9.989896189228491</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8526870150368921</v>
+        <v>-0.8544058095870328</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.286986720586252</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.91212937118569</v>
+        <v>-9.916426357561042</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8079273808764915</v>
+        <v>-0.8096461754266322</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.213516888918803</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.08725378857223</v>
+        <v>-10.09155077494759</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8634219270835919</v>
+        <v>-0.8651407216337326</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.388641306305347</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.32170588258672</v>
+        <v>-10.32600286896207</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9644219295909839</v>
+        <v>-0.9661407241411246</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.388641306305347</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.60950972712396</v>
+        <v>-10.61380671349931</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.086215658179855</v>
+        <v>-1.087934452729996</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.676445150842585</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.66229588272429</v>
+        <v>-10.66659286909964</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.10621433058143</v>
+        <v>-1.10793312513157</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.772120637424982</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.89432480246055</v>
+        <v>-10.8986217888359</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.19633216984682</v>
+        <v>-1.19805096439696</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.834133334613405</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.84230928849174</v>
+        <v>-10.84660627486709</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.171535628572894</v>
+        <v>-1.173254423123034</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.834133334613405</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.98398113021586</v>
+        <v>-10.98827811659121</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.229679592161284</v>
+        <v>-1.231398386711424</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.834133334613405</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.93439028579102</v>
+        <v>-10.93868727216637</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.194789844226478</v>
+        <v>-1.196508638776618</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.784542490188572</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.73523817855392</v>
+        <v>-10.73953516492928</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.128180134978321</v>
+        <v>-1.129898929528462</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.619219964238758</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.50939302583451</v>
+        <v>-10.51369001220986</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.028263000854348</v>
+        <v>-1.029981795404488</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.577293288651595</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.38481436949692</v>
+        <v>-10.38911135587227</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9772923937632521</v>
+        <v>-0.9790111883133927</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.577293288651595</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.43770965754121</v>
+        <v>-10.44200664391656</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9958167348188587</v>
+        <v>-0.9975355293689994</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.572337942563149</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.15380092661246</v>
+        <v>-10.15809791298781</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.876519538208723</v>
+        <v>-0.8782383327588636</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.572337942563149</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.08243453400281</v>
+        <v>-10.08673152037816</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8577102435587296</v>
+        <v>-0.8594290381088694</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.500971549953501</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.818597666798741</v>
+        <v>-9.822894653174092</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7620589779900091</v>
+        <v>-0.7637777725401493</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.500971549953501</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.551355865930343</v>
+        <v>-9.555652852305695</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6569968181420234</v>
+        <v>-0.6587156126921641</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.500971549953501</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.453448827253853</v>
+        <v>-9.457745813629204</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6181343176448881</v>
+        <v>-0.6198531121950288</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.432985800092944</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.429495286277895</v>
+        <v>-9.433792272653246</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6078843951090112</v>
+        <v>-0.6096031896591518</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.409032259116987</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.165435347955098</v>
+        <v>-9.169732334330449</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5155207359416449</v>
+        <v>-0.5172395304917852</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.144972320794191</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.458355724450261</v>
+        <v>-8.462652710825612</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2354759202000105</v>
+        <v>-0.2371947147501512</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.144972320794191</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.41817142608407</v>
+        <v>-8.422468412459422</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.219058576965693</v>
+        <v>-0.2207773715158337</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.104788022428</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.338101630546266</v>
+        <v>-8.342398616921617</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1876638375298145</v>
+        <v>-0.1893826320799548</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.024718226890196</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.104620408316666</v>
+        <v>-8.108917394692018</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.0863469198001221</v>
+        <v>-0.08806571435026278</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.791237004660597</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.954954017309151</v>
+        <v>-7.959251003684503</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.0293725737100754</v>
+        <v>-0.03109136826021608</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.698333513418061</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.822678543678265</v>
+        <v>-7.826975530053616</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.0189051024893061</v>
+        <v>0.01718630793916587</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.566058039787175</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.632078869005112</v>
+        <v>-7.636375855380463</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.09796003304620404</v>
+        <v>0.09624123849606336</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.375458365114022</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.383079070321531</v>
+        <v>-7.387376056696882</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2104662937432953</v>
+        <v>0.2087474991931546</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.375458365114022</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.488669060094636</v>
+        <v>-7.492966046469987</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.04025436823483464</v>
+        <v>0.03853557368469396</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.481048354887126</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.507403962213233</v>
+        <v>-7.511700948588584</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.08130474926448228</v>
+        <v>0.0795859547143416</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.481048354887126</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.359463920805633</v>
+        <v>-7.363760907180985</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.02060184313935443</v>
+        <v>0.01888304858921375</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.460727438978569</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.335235284416661</v>
+        <v>-7.339532270792012</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.02157931144146508</v>
+        <v>0.01986051689132484</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.436498802589596</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.29168687764597</v>
+        <v>-7.295983864021322</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.0320380620546481</v>
+        <v>0.03031926750450786</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.436498802589596</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.049538484192112</v>
+        <v>-7.053835470567464</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1433597738173344</v>
+        <v>0.1416409792671942</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.436498802589596</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.986309112423764</v>
+        <v>-6.990606098799115</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1631836429838689</v>
+        <v>0.1614648484337282</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.436498802589596</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.863017977606633</v>
+        <v>-6.867314963981984</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.209998190921298</v>
+        <v>0.2082793963711578</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.313207667772466</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.84186877870319</v>
+        <v>-6.846165765078541</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2261588487200008</v>
+        <v>0.2244400541698601</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.292058468869023</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.598103336719745</v>
+        <v>-6.602400323095097</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3194457338604288</v>
+        <v>0.3177269393102886</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.292058468869023</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.451206309001876</v>
+        <v>-6.455503295377227</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.380328858867593</v>
+        <v>0.3786100643174524</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.244400226890435</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.201355915052801</v>
+        <v>-6.205652901428152</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4730110914309251</v>
+        <v>0.4712922968807844</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.244400226890435</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.025463822585369</v>
+        <v>-6.02976080896072</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5469670519385463</v>
+        <v>0.5452482573884061</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.244400226890435</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.854017359562905</v>
+        <v>-5.858314345938257</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6288731432020858</v>
+        <v>0.6271543486519451</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.072953763867972</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.628984359894083</v>
+        <v>-5.633281346269434</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7179068206859118</v>
+        <v>0.7161880261357711</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8479207641991487</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.565348617660148</v>
+        <v>-5.569645604035499</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7480559186338027</v>
+        <v>0.7463371240836625</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7842850219652142</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.47234857645425</v>
+        <v>-5.476645562829601</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7664501938999577</v>
+        <v>0.7647313993498175</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7842850219652142</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.23191807964939</v>
+        <v>-5.236215066024741</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8643654692467795</v>
+        <v>0.8626466746966388</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5438545251603539</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.159675511478195</v>
+        <v>-5.163972497853546</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8971918103500776</v>
+        <v>0.8954730157999369</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5438545251603539</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.04373566185301</v>
+        <v>-5.048032648228361</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9442463341174916</v>
+        <v>0.9425275395673509</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.46703279414423</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.801080073429846</v>
+        <v>-4.805377059805197</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.03830664070675</v>
+        <v>1.03658784615661</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.46703279414423</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.581059275392835</v>
+        <v>-4.585356261768187</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.127893996932169</v>
+        <v>1.126175202382028</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.3258129490762498</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.448191586329558</v>
+        <v>-4.452488572704909</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.196935255359303</v>
+        <v>1.195216460809163</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.3258129490762498</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.288676482810188</v>
+        <v>-4.292973469185539</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.261887141207353</v>
+        <v>1.260168346657212</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.1662978455568799</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.144004337710451</v>
+        <v>-4.148301324085802</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.329844101808688</v>
+        <v>1.328125307258547</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.02162570045714246</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.203879165068143</v>
+        <v>-4.208176151443494</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.291931662267037</v>
+        <v>1.290212867716896</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.08150052781483458</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.117079667289135</v>
+        <v>-4.121376653664486</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.349051954701206</v>
+        <v>1.347333160151066</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.08150052781483458</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.119549373750941</v>
+        <v>-4.123846360126292</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.348136473489896</v>
+        <v>1.346417678939755</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.08397023427664074</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.187919560074951</v>
+        <v>-4.192216546450302</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.331795321434994</v>
+        <v>1.330076526884853</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.0746945352404258</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.066503130448474</v>
+        <v>-4.070800116823825</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.370798601917476</v>
+        <v>1.369079807367335</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.0746945352404258</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.09749628977718</v>
+        <v>-4.101793276152531</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.18311090322638</v>
+        <v>1.18139210867624</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.0746945352404258</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.92202202998471</v>
+        <v>-3.926319016360062</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.257867839135156</v>
+        <v>1.256149044585015</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.0746945352404258</v>
@@ -46171,10 +46171,10 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.032958282625959</v>
+        <v>-4.03725526900131</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.189235366839863</v>
+        <v>1.187516572289723</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.0746945352404258</v>
@@ -46194,10 +46194,10 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.235984860169192</v>
+        <v>-4.240281846544543</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.111156121042476</v>
+        <v>1.109437326492335</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2777211127836592</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.078059261233899</v>
+        <v>-4.08235624760925</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.184498747048725</v>
+        <v>1.182779952498585</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2777211127836592</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.991815798207521</v>
+        <v>-3.996112784582873</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.213942402833137</v>
+        <v>1.212223608282996</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2777211127836592</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.992998882858582</v>
+        <v>-3.997295869233934</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.205244944417238</v>
+        <v>1.203526149867097</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2833641612501707</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.869871175864499</v>
+        <v>-3.87416816223985</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.255047900247973</v>
+        <v>1.253329105697832</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2833641612501707</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.77706069441364</v>
+        <v>-3.781357680788991</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.221444784719682</v>
+        <v>1.219725990169542</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1905536797993114</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.728497642192609</v>
+        <v>-3.732794628567961</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.242743481532695</v>
+        <v>1.241024686982555</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.1419906275782812</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.615826423956359</v>
+        <v>-3.62012341033171</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.282887677338918</v>
+        <v>1.281168882788778</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.02931940934203098</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.503449422773687</v>
+        <v>-3.507746409149038</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.333329773642654</v>
+        <v>1.331610979092514</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.02931940934203098</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.701683991660417</v>
+        <v>-3.705980978035768</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.265533147856501</v>
+        <v>1.263814353306361</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.2275539782287616</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.784685272685696</v>
+        <v>-3.788982259061047</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.070688355447043</v>
+        <v>1.068969560896903</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.2461248627559353</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.62549100062912</v>
+        <v>-3.629787987004471</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.254515724988879</v>
+        <v>1.252796930438739</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.2461248627559353</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.712089583610223</v>
+        <v>-3.716386569985574</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.234389317898761</v>
+        <v>1.232670523348621</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.2461248627559353</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.673705921052071</v>
+        <v>-3.678002907427423</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.24716222426439</v>
+        <v>1.24544342971425</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.2077412001977841</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.496589591016905</v>
+        <v>-3.500886577392257</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.314737785123758</v>
+        <v>1.313018990573618</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.2077412001977841</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.466887467040612</v>
+        <v>-3.471184453415963</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.327302026476189</v>
+        <v>1.325583231926049</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.2122113254130975</v>
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.497901787404992</v>
+        <v>-3.291809032177195</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.308683273636851</v>
+        <v>1.39112037572797</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2480455753649109</v>
+        <v>-0.05543456724237883</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.559373067693649</v>
+        <v>2.674939672567168</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.542916000925598</v>
+        <v>-3.336823245697801</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.271485043560199</v>
+        <v>1.353922145651318</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2783944706795155</v>
+        <v>-0.08578346255698344</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.521971185836476</v>
+        <v>2.637537790709995</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.809920511198033</v>
+        <v>-3.603827755970237</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.17037480179017</v>
+        <v>1.252811903881289</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4727575087224641</v>
+        <v>-0.280146500599932</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.411044925349653</v>
+        <v>2.526611530223172</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.098707731656948</v>
+        <v>-3.892614976429152</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.054063835503106</v>
+        <v>1.136500937594224</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5738436288214644</v>
+        <v>-0.3812326206989324</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.349597175186754</v>
+        <v>2.465163780060273</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.066232145486176</v>
+        <v>-3.86013939025838</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.064654031525731</v>
+        <v>1.14709113361685</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.5738436288214644</v>
+        <v>-0.3812326206989324</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.34719713674107</v>
+        <v>2.46276374161459</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.047194017778879</v>
+        <v>-3.841101262551082</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.068794001816895</v>
+        <v>1.151231103908014</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.632027240152659</v>
+        <v>-0.4394162320301269</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.308811689150599</v>
+        <v>2.424378294024118</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.063939883035254</v>
+        <v>-3.857847127807458</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.239677524653026</v>
+        <v>1.322114626744144</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.632027240152659</v>
+        <v>-0.4394162320301269</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.486393558089279</v>
+        <v>2.601960162962799</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.116260263636046</v>
+        <v>-3.910167508408249</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.219582701398843</v>
+        <v>1.302019803489961</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5970803801437868</v>
+        <v>-0.4044693720212548</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.508195003080736</v>
+        <v>2.623761607954255</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.260583169560965</v>
+        <v>-4.054490414333168</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.167862069425801</v>
+        <v>1.250299171516919</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5970803801437868</v>
+        <v>-0.4044693720212548</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.514203533477662</v>
+        <v>2.629770138351181</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.112840199325962</v>
+        <v>-3.906747444098166</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.306111905311824</v>
+        <v>1.388549007402942</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.4292730229089037</v>
+        <v>-0.2366620147863716</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.694040595610614</v>
+        <v>2.809607200484133</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.214854881857184</v>
+        <v>-4.008762126629387</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.268099653830816</v>
+        <v>1.350536755921935</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.4292730229089037</v>
+        <v>-0.2366620147863716</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.696834217142095</v>
+        <v>2.812400822015614</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,13 +46815,13 @@
         <v>3.109708608571037</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.214854881857184</v>
+        <v>-4.008762126629387</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.268099653830816</v>
+        <v>1.350536755921935</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4292730229089037</v>
+        <v>-0.2366620147863716</v>
       </c>
       <c r="G1968" t="n">
         <v>3.102772405557405</v>

--- a/tame_output/ON/bt/strategyON_20240518.xlsx
+++ b/tame_output/ON/bt/strategyON_20240518.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>47.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>127.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.9%</t>
+          <t>448.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.4%</t>
+          <t>-568.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-241.2%</t>
+          <t>-243.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-93.5%</t>
+          <t>-112.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.7%</t>
+          <t>-249.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-135.7%</t>
+          <t>-146.7%</t>
         </is>
       </c>
     </row>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.472502113040866</v>
+        <v>-7.580842483270056</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1295214241625948</v>
+        <v>0.08618527607091897</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.818376935025675</v>
+        <v>-7.839189753043014</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.01272893948563381</v>
+        <v>-0.02105406669256915</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.98195681321006</v>
+        <v>-8.002769631227398</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.07975597070438623</v>
+        <v>-0.08808109791132201</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.278618155020258</v>
+        <v>-8.299430973037596</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1946415314992573</v>
+        <v>-0.2029666587061931</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.401862544235687</v>
+        <v>-8.422675362253026</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2479655917198325</v>
+        <v>-0.2562907189267678</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.784863932978318</v>
+        <v>-8.805676750995657</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4012682485384689</v>
+        <v>-0.4095933757454042</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.942262813191439</v>
+        <v>-8.963075631208778</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4616562846522871</v>
+        <v>-0.4699814118592225</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.301793135695441</v>
+        <v>-9.322605953712779</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6001181103558375</v>
+        <v>-0.6084432375627729</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.352142199149663</v>
+        <v>-9.372955017167001</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.612341715780349</v>
+        <v>-0.6206668429872844</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.57129116722386</v>
+        <v>-9.592103985241199</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6969595523882588</v>
+        <v>-0.7052846795951946</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.984577007876364</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.567600242267449</v>
+        <v>-9.588413060284788</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6954831824056948</v>
+        <v>-0.7038083096126302</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.984577007876364</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.771858417597313</v>
+        <v>-9.792671235614652</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7716732554189978</v>
+        <v>-0.7799983826259331</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.112215952490353</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.989896189228491</v>
+        <v>-10.01070900724583</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8544058095870328</v>
+        <v>-0.8627309367939682</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.286986720586252</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.916426357561042</v>
+        <v>-9.93723917557838</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8096461754266322</v>
+        <v>-0.8179713026335675</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.213516888918803</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.09155077494759</v>
+        <v>-10.11236359296492</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8651407216337326</v>
+        <v>-0.8734658488406684</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.388641306305347</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.32600286896207</v>
+        <v>-10.34681568697941</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9661407241411246</v>
+        <v>-0.9744658513480595</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.388641306305347</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.61380671349931</v>
+        <v>-10.63461953151665</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.087934452729996</v>
+        <v>-1.096259579936932</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.676445150842585</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.66659286909964</v>
+        <v>-10.68740568711698</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.10793312513157</v>
+        <v>-1.116258252338506</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.772120637424982</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.8986217888359</v>
+        <v>-10.91943460685324</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.19805096439696</v>
+        <v>-1.206376091603896</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.834133334613405</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.84660627486709</v>
+        <v>-10.86741909288443</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.173254423123034</v>
+        <v>-1.18157955032997</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.834133334613405</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.98827811659121</v>
+        <v>-11.00909093460855</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.231398386711424</v>
+        <v>-1.23972351391836</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.834133334613405</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.93868727216637</v>
+        <v>-10.95950009018371</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.196508638776618</v>
+        <v>-1.204833765983553</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.784542490188572</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.73953516492928</v>
+        <v>-10.76034798294661</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.129898929528462</v>
+        <v>-1.138224056735397</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.619219964238758</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.51369001220986</v>
+        <v>-10.5345028302272</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.029981795404488</v>
+        <v>-1.038306922611425</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.577293288651595</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.38911135587227</v>
+        <v>-10.40992417388961</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9790111883133927</v>
+        <v>-0.9873363155203285</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.577293288651595</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.44200664391656</v>
+        <v>-10.4628194619339</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9975355293689994</v>
+        <v>-1.005860656575936</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.572337942563149</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.15809791298781</v>
+        <v>-10.17891073100515</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8782383327588636</v>
+        <v>-0.8865634599657994</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.572337942563149</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.08673152037816</v>
+        <v>-10.1075443383955</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8594290381088694</v>
+        <v>-0.8677541653158061</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.500971549953501</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.822894653174092</v>
+        <v>-9.843707471191433</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7637777725401493</v>
+        <v>-0.7721028997470856</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.500971549953501</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.555652852305695</v>
+        <v>-9.576465670323035</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6587156126921641</v>
+        <v>-0.6670407398991003</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.500971549953501</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.457745813629204</v>
+        <v>-9.478558631646544</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6198531121950288</v>
+        <v>-0.6281782394019646</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.432985800092944</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.433792272653246</v>
+        <v>-9.454605090670587</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6096031896591518</v>
+        <v>-0.6179283168660881</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.409032259116987</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.169732334330449</v>
+        <v>-9.19054515234779</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5172395304917852</v>
+        <v>-0.5255646576987214</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.144972320794191</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.462652710825612</v>
+        <v>-8.483465528842952</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2371947147501512</v>
+        <v>-0.2455198419570874</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.144972320794191</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.422468412459422</v>
+        <v>-8.443281230476762</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2207773715158337</v>
+        <v>-0.2291024987227699</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.104788022428</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.342398616921617</v>
+        <v>-8.363211434938957</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1893826320799548</v>
+        <v>-0.197707759286891</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.024718226890196</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.108917394692018</v>
+        <v>-8.129730212709358</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.08806571435026278</v>
+        <v>-0.09639084155719901</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.791237004660597</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.959251003684503</v>
+        <v>-7.980063821701843</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.03109136826021608</v>
+        <v>-0.03941649546715187</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.698333513418061</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.826975530053616</v>
+        <v>-7.847788348070956</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.01718630793916587</v>
+        <v>0.008861180732229634</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.566058039787175</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.636375855380463</v>
+        <v>-7.657188673397804</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.09624123849606336</v>
+        <v>0.08791611128912713</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.375458365114022</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.387376056696882</v>
+        <v>-7.408188874714223</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2087474991931546</v>
+        <v>0.2004223719862184</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.375458365114022</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.492966046469987</v>
+        <v>-7.513778864487327</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.03853557368469396</v>
+        <v>0.03021044647775817</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.481048354887126</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.511700948588584</v>
+        <v>-7.532513766605924</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.0795859547143416</v>
+        <v>0.07126082750740537</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.481048354887126</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.363760907180985</v>
+        <v>-7.384573725198325</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.01888304858921375</v>
+        <v>0.01055792138227751</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.460727438978569</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.339532270792012</v>
+        <v>-7.360345088809352</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.01986051689132484</v>
+        <v>0.01153538968438861</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.436498802589596</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.295983864021322</v>
+        <v>-7.316796682038662</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.03031926750450786</v>
+        <v>0.02199414029757163</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.436498802589596</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.053835470567464</v>
+        <v>-7.074648288584804</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1416409792671942</v>
+        <v>0.133315852060258</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.436498802589596</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.990606098799115</v>
+        <v>-7.011418916816456</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1614648484337282</v>
+        <v>0.1531397212267924</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.436498802589596</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.867314963981984</v>
+        <v>-6.888127781999325</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2082793963711578</v>
+        <v>0.1999542691642215</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.313207667772466</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.846165765078541</v>
+        <v>-6.866978583095881</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2244400541698601</v>
+        <v>0.2161149269629239</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.292058468869023</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.602400323095097</v>
+        <v>-6.623213141112437</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3177269393102886</v>
+        <v>0.3094018121033524</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.292058468869023</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.455503295377227</v>
+        <v>-6.476316113394567</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3786100643174524</v>
+        <v>0.3702849371105161</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.244400226890435</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.205652901428152</v>
+        <v>-6.226465719445493</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4712922968807844</v>
+        <v>0.4629671696738482</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.244400226890435</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.02976080896072</v>
+        <v>-6.050573626978061</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5452482573884061</v>
+        <v>0.5369231301814699</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.244400226890435</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.858314345938257</v>
+        <v>-5.879127163955597</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6271543486519451</v>
+        <v>0.6188292214450088</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.072953763867972</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.633281346269434</v>
+        <v>-5.654094164286774</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7161880261357711</v>
+        <v>0.7078628989288354</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8479207641991487</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.569645604035499</v>
+        <v>-5.59045842205284</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7463371240836625</v>
+        <v>0.7380119968767263</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7842850219652142</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.476645562829601</v>
+        <v>-5.497458380846941</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7647313993498175</v>
+        <v>0.7564062721428813</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7842850219652142</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.236215066024741</v>
+        <v>-5.257027884042081</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8626466746966388</v>
+        <v>0.8543215474897026</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5438545251603539</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.163972497853546</v>
+        <v>-5.184785315870887</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8954730157999369</v>
+        <v>0.8871478885930006</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5438545251603539</v>
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.048032648228361</v>
+        <v>-5.105876217122001</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9425275395673509</v>
+        <v>0.9193901120098951</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.46703279414423</v>
+        <v>-0.4817777259186707</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.681877346685905</v>
+        <v>2.673030387621241</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.805377059805197</v>
+        <v>-4.863220628698837</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.03658784615661</v>
+        <v>1.013450418599154</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.46703279414423</v>
+        <v>-0.4817777259186707</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.678875417905898</v>
+        <v>2.670028458841234</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.585356261768187</v>
+        <v>-4.643199830661827</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.126175202382028</v>
+        <v>1.103037774824572</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3258129490762498</v>
+        <v>-0.3405578808506905</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.7651863619573</v>
+        <v>2.756339402892636</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.452488572704909</v>
+        <v>-4.510332141598549</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.195216460809163</v>
+        <v>1.172079033251707</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3258129490762498</v>
+        <v>-0.3405578808506905</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.781080544759124</v>
+        <v>2.77223358569446</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.292973469185539</v>
+        <v>-4.350817038079179</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.260168346657212</v>
+        <v>1.237030919099757</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1662978455568799</v>
+        <v>-0.1810427773313206</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.877935451311048</v>
+        <v>2.869088492246383</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.148301324085802</v>
+        <v>-4.206144892979442</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.328125307258547</v>
+        <v>1.304987879701091</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.02162570045714246</v>
+        <v>-0.03637063223158316</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.97482684093233</v>
+        <v>2.965979881867665</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.208176151443494</v>
+        <v>-4.266019720337134</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.290212867716896</v>
+        <v>1.26707544015944</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.08150052781483458</v>
+        <v>-0.09624545958927527</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.924939435919141</v>
+        <v>2.916092476854476</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.121376653664486</v>
+        <v>-4.179220222558126</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.347333160151066</v>
+        <v>1.32419573259361</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.08150052781483458</v>
+        <v>-0.09624545958927527</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.947339929241707</v>
+        <v>2.938492970177042</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.123846360126292</v>
+        <v>-4.181689929019932</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.346417678939755</v>
+        <v>1.323280251382299</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.08397023427664074</v>
+        <v>-0.09871516605108144</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.945930506738035</v>
+        <v>2.937083547673371</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.192216546450302</v>
+        <v>-4.250060115343942</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.330076526884853</v>
+        <v>1.306939099327397</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.08943946701486649</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.962502848634466</v>
+        <v>2.953655889569802</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.070800116823825</v>
+        <v>-4.128643685717465</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.369079807367335</v>
+        <v>1.345942379809879</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.08943946701486649</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.952939557266357</v>
+        <v>2.944092598201693</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.101793276152531</v>
+        <v>-4.159636845046171</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.18139210867624</v>
+        <v>1.158254681118784</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.08943946701486649</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.777649122306744</v>
+        <v>2.76880216324208</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675897</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.926319016360062</v>
+        <v>-3.984162585253701</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.256149044585015</v>
+        <v>1.233011617027559</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.08943946701486649</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.782216354298532</v>
+        <v>2.773369395233868</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.03725526900131</v>
+        <v>-4.09509883789495</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.187516572289723</v>
+        <v>1.164379144732267</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.08943946701486649</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.757958383059739</v>
+        <v>2.749111423995075</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581288</v>
+        <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.240281846544543</v>
+        <v>-4.298125415438183</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.109437326492335</v>
+        <v>1.086299898934879</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.2924660445580999</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.639273821753704</v>
+        <v>2.63042686268904</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734157</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.08235624760925</v>
+        <v>-4.14019981650289</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.182779952498585</v>
+        <v>1.159642524941129</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.2924660445580999</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.649446208185837</v>
+        <v>2.640599249121172</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212293</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.996112784582873</v>
+        <v>-4.053956353476512</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.212223608282996</v>
+        <v>1.18908618072554</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.2924660445580999</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.644392478759698</v>
+        <v>2.635545519695033</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786041</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.997295869233934</v>
+        <v>-4.055139438127574</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.203526149867097</v>
+        <v>1.180388722309641</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2833641612501707</v>
+        <v>-0.2981090930246114</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.632782425124316</v>
+        <v>2.623935466059652</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.87416816223985</v>
+        <v>-3.932011731133491</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.253329105697832</v>
+        <v>1.230191678140376</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2833641612501707</v>
+        <v>-0.2981090930246114</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.633334298157417</v>
+        <v>2.624487339092753</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.781357680788991</v>
+        <v>-3.839201249682632</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.219725990169542</v>
+        <v>1.196588562612085</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1905536797993114</v>
+        <v>-0.2052986115737521</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.618293278919299</v>
+        <v>2.609446319854634</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.732794628567961</v>
+        <v>-3.790638197461601</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.241024686982555</v>
+        <v>1.217887259425098</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1419906275782812</v>
+        <v>-0.1567355593527219</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.649304586176518</v>
+        <v>2.640457627111853</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.62012341033171</v>
+        <v>-3.677966979225351</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.281168882788778</v>
+        <v>1.258031455231321</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.02931940934203098</v>
+        <v>-0.04406434111647167</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.711983025629991</v>
+        <v>2.703136066565326</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.507746409149038</v>
+        <v>-3.565589978042679</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.331610979092514</v>
+        <v>1.308473551535058</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.02931940934203098</v>
+        <v>-0.04406434111647167</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.717474321460658</v>
+        <v>2.708627362395994</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968859</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.705980978035768</v>
+        <v>-3.763824546929409</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.263814353306361</v>
+        <v>1.240676925748905</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2275539782287616</v>
+        <v>-0.2422989100032023</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.610030781897159</v>
+        <v>2.601183822832494</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175319</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.788982259061047</v>
+        <v>-3.846825827954688</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.068969560896903</v>
+        <v>1.045832133339446</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.260869794530376</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.437243971181508</v>
+        <v>2.428397012116843</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199266</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.629787987004471</v>
+        <v>-3.687631555898112</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.252796930438739</v>
+        <v>1.229659502881282</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.260869794530376</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.557393631900713</v>
+        <v>2.548546672836049</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660765</v>
+        <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.716386569985574</v>
+        <v>-3.774230138879215</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.232670523348621</v>
+        <v>1.209533095791164</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.260869794530376</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.571906658003036</v>
+        <v>2.563059698938372</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383421</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.678002907427423</v>
+        <v>-3.735846476321063</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.24544342971425</v>
+        <v>1.222306002156793</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2077412001977841</v>
+        <v>-0.2224861319722248</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.592356296880296</v>
+        <v>2.583509337815631</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002481</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.500886577392257</v>
+        <v>-3.558730146285897</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.313018990573618</v>
+        <v>1.289881563016162</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2077412001977841</v>
+        <v>-0.2224861319722248</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.589085325725598</v>
+        <v>2.580238366660933</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263899</v>
+        <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.471184453415963</v>
+        <v>-3.529028022309604</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.325583231926049</v>
+        <v>1.302445804368592</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2122113254130975</v>
+        <v>-0.2269562571875382</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.587086642358323</v>
+        <v>2.578239683293658</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481232</v>
+        <v>3.750725801481234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.291809032177195</v>
+        <v>-3.349652601070836</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.39112037572797</v>
+        <v>1.367982948170514</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.05543456724237883</v>
+        <v>-0.07017949901681952</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.674939672567168</v>
+        <v>2.666092713502504</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452227</v>
+        <v>3.716988143452229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.336823245697801</v>
+        <v>-3.394666814591442</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.353922145651318</v>
+        <v>1.330784718093861</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.08578346255698344</v>
+        <v>-0.1005283943314241</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.637537790709995</v>
+        <v>2.628690831645331</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979534</v>
+        <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.603827755970237</v>
+        <v>-3.661671324863877</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.252811903881289</v>
+        <v>1.229674476323833</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.280146500599932</v>
+        <v>-0.2948914323743727</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.526611530223172</v>
+        <v>2.517764571158508</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230807</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.892614976429152</v>
+        <v>-3.950458545322793</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.136500937594224</v>
+        <v>1.113363510036768</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.3959775524733731</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.465163780060273</v>
+        <v>2.456316820995609</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285451</v>
+        <v>3.705568086285453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.86013939025838</v>
+        <v>-3.91798295915202</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.14709113361685</v>
+        <v>1.123953706059394</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.3959775524733731</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.46276374161459</v>
+        <v>2.453916782549925</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848099</v>
+        <v>3.709506867848101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.841101262551082</v>
+        <v>-3.898944831444723</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.151231103908014</v>
+        <v>1.128093676350558</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.4541611638045676</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.424378294024118</v>
+        <v>2.415531334959454</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.857847127807458</v>
+        <v>-3.915690696701098</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.322114626744144</v>
+        <v>1.298977199186688</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.4541611638045676</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.601960162962799</v>
+        <v>2.593113203898134</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537862</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.910167508408249</v>
+        <v>-3.96801107730189</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.302019803489961</v>
+        <v>1.278882375932505</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.4192143037956955</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.623761607954255</v>
+        <v>2.614914648889591</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259121</v>
+        <v>3.787422005259122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.054490414333168</v>
+        <v>-4.112333983226809</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.250299171516919</v>
+        <v>1.227161743959463</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.4192143037956955</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.629770138351181</v>
+        <v>2.620923179286517</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989906</v>
+        <v>3.781497674989907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.906747444098166</v>
+        <v>-3.964591012991807</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.388549007402942</v>
+        <v>1.365411579845486</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.2514069465608123</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.809607200484133</v>
+        <v>2.800760241419469</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651168</v>
+        <v>3.80224235365117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.008762126629387</v>
+        <v>-4.066605695523028</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.350536755921935</v>
+        <v>1.327399328364478</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.2514069465608123</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.812400822015614</v>
+        <v>2.80355386295095</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.822680306802603</v>
+        <v>3.755531662824992</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.109708608571037</v>
+        <v>3.00026504071572</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.008762126629387</v>
+        <v>-4.066605695523028</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.350536755921935</v>
+        <v>1.327399328364478</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.2514069465608123</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.102772405557405</v>
+        <v>2.993328837702088</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240518.xlsx
+++ b/tame_output/ON/bt/strategyON_20240518.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>55.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-16.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>110.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>128.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-52.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-72.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-568.2%</t>
+          <t>-578.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-41.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-38.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-243.5%</t>
+          <t>-247.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.6%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-112.0%</t>
+          <t>-91.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-249.1%</t>
+          <t>-257.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-146.7%</t>
+          <t>-170.7%</t>
         </is>
       </c>
     </row>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.839189753043014</v>
+        <v>-7.926717305254865</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.02105406669256915</v>
+        <v>-0.05606508757730966</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.002769631227398</v>
+        <v>-8.139039068395125</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.08808109791132201</v>
+        <v>-0.1425888727784126</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.299430973037596</v>
+        <v>-8.435700410205323</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2029666587061931</v>
+        <v>-0.2574744335732837</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.422675362253026</v>
+        <v>-8.558944799420752</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2562907189267678</v>
+        <v>-0.3107984937938584</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.805676750995657</v>
+        <v>-8.941946188163383</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4095933757454042</v>
+        <v>-0.4641011506124948</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.963075631208778</v>
+        <v>-9.099345068376504</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4699814118592225</v>
+        <v>-0.5244891867263131</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.322605953712779</v>
+        <v>-9.458875390880506</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6084432375627729</v>
+        <v>-0.6629510124298634</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.372955017167001</v>
+        <v>-9.509224454334728</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6206668429872844</v>
+        <v>-0.6751746178543749</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.592103985241199</v>
+        <v>-9.728373422408925</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7052846795951946</v>
+        <v>-0.7597924544622852</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.984577007876364</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.588413060284788</v>
+        <v>-9.724682497452514</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7038083096126302</v>
+        <v>-0.7583160844797208</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.984577007876364</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.792671235614652</v>
+        <v>-9.928940672782378</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7799983826259331</v>
+        <v>-0.8345061574930237</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.112215952490353</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.01070900724583</v>
+        <v>-10.14697844441356</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8627309367939682</v>
+        <v>-0.9172387116610587</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.286986720586252</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.93723917557838</v>
+        <v>-10.07350861274611</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8179713026335675</v>
+        <v>-0.8724790775006577</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.213516888918803</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.11236359296492</v>
+        <v>-10.24863303013265</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8734658488406684</v>
+        <v>-0.9279736237077589</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.388641306305347</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.34681568697941</v>
+        <v>-10.48308512414714</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9744658513480595</v>
+        <v>-1.02897362621515</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.388641306305347</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.63461953151665</v>
+        <v>-10.77088896868438</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.096259579936932</v>
+        <v>-1.150767354804022</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.676445150842585</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.68740568711698</v>
+        <v>-10.8236751242847</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.116258252338506</v>
+        <v>-1.170766027205596</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.772120637424982</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.91943460685324</v>
+        <v>-11.05570404402097</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.206376091603896</v>
+        <v>-1.260883866470987</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.834133334613405</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.86741909288443</v>
+        <v>-11.00368853005215</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.18157955032997</v>
+        <v>-1.236087325197061</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.834133334613405</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.00909093460855</v>
+        <v>-11.14536037177627</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.23972351391836</v>
+        <v>-1.294231288785451</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.834133334613405</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.95950009018371</v>
+        <v>-11.09576952735144</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.204833765983553</v>
+        <v>-1.259341540850644</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.784542490188572</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.76034798294661</v>
+        <v>-10.89661742011434</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.138224056735397</v>
+        <v>-1.192731831602488</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.619219964238758</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.5345028302272</v>
+        <v>-10.67077226739493</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.038306922611425</v>
+        <v>-1.092814697478515</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.577293288651595</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.40992417388961</v>
+        <v>-10.54619361105734</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9873363155203285</v>
+        <v>-1.041844090387419</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.577293288651595</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.4628194619339</v>
+        <v>-10.59908889910163</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.005860656575936</v>
+        <v>-1.060368431443027</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.572337942563149</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.17891073100515</v>
+        <v>-10.31518016817288</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8865634599657994</v>
+        <v>-0.94107123483289</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.572337942563149</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.1075443383955</v>
+        <v>-10.24381377556323</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8677541653158061</v>
+        <v>-0.9222619401828966</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.500971549953501</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.843707471191433</v>
+        <v>-9.979976908359159</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7721028997470856</v>
+        <v>-0.8266106746141761</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.500971549953501</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.576465670323035</v>
+        <v>-9.712735107490762</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6670407398991003</v>
+        <v>-0.7215485147661909</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.500971549953501</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.478558631646544</v>
+        <v>-9.614828068814271</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6281782394019646</v>
+        <v>-0.6826860142690552</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.432985800092944</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.454605090670587</v>
+        <v>-9.590874527838313</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6179283168660881</v>
+        <v>-0.6724360917331786</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.409032259116987</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.19054515234779</v>
+        <v>-9.326814589515516</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5255646576987214</v>
+        <v>-0.580072432565812</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.144972320794191</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.483465528842952</v>
+        <v>-8.619734966010679</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2455198419570874</v>
+        <v>-0.300027616824178</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.144972320794191</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.443281230476762</v>
+        <v>-8.579550667644488</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2291024987227699</v>
+        <v>-0.2836102735898605</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.104788022428</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.363211434938957</v>
+        <v>-8.499480872106684</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.197707759286891</v>
+        <v>-0.2522155341539816</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.024718226890196</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.129730212709358</v>
+        <v>-8.265999649877084</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.09639084155719901</v>
+        <v>-0.1508986164242896</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.791237004660597</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.980063821701843</v>
+        <v>-8.11633325886957</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.03941649546715187</v>
+        <v>-0.09392427033424289</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.698333513418061</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.847788348070956</v>
+        <v>-7.984057785238684</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.008861180732229634</v>
+        <v>-0.04564659413486138</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.566058039787175</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.657188673397804</v>
+        <v>-7.793458110565531</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.08791611128912713</v>
+        <v>0.03340833642203656</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.375458365114022</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.408188874714223</v>
+        <v>-7.54445831188195</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2004223719862184</v>
+        <v>0.1459145971191274</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.375458365114022</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.513778864487327</v>
+        <v>-7.650048301655055</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.03021044647775817</v>
+        <v>-0.02429732838933285</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.481048354887126</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.532513766605924</v>
+        <v>-7.668783203773652</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.07126082750740537</v>
+        <v>0.01675305264031479</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.481048354887126</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.384573725198325</v>
+        <v>-7.520843162366052</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.01055792138227751</v>
+        <v>-0.04394985348481306</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.460727438978569</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.360345088809352</v>
+        <v>-7.49661452597708</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.01153538968438861</v>
+        <v>-0.04297238518270241</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.436498802589596</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.316796682038662</v>
+        <v>-7.453066119206389</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.02199414029757163</v>
+        <v>-0.03251363456951939</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.436498802589596</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.074648288584804</v>
+        <v>-7.210917725752531</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.133315852060258</v>
+        <v>0.07880807719316696</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.436498802589596</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.011418916816456</v>
+        <v>-7.147688353984183</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1531397212267924</v>
+        <v>0.09863194635970141</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.436498802589596</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.888127781999325</v>
+        <v>-7.024397219167052</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1999542691642215</v>
+        <v>0.1454464942971305</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.313207667772466</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.866978583095881</v>
+        <v>-7.003248020263609</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2161149269629239</v>
+        <v>0.1616071520958329</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.292058468869023</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.623213141112437</v>
+        <v>-6.759482578280164</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3094018121033524</v>
+        <v>0.2548940372362614</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.292058468869023</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.476316113394567</v>
+        <v>-6.612585550562294</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3702849371105161</v>
+        <v>0.3157771622434256</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.244400226890435</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.226465719445493</v>
+        <v>-6.362735156613219</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4629671696738482</v>
+        <v>0.4084593948067576</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.244400226890435</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.050573626978061</v>
+        <v>-6.186843064145787</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5369231301814699</v>
+        <v>0.4824153553143793</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.244400226890435</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.879127163955597</v>
+        <v>-6.015396601123324</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6188292214450088</v>
+        <v>0.5643214465779183</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.072953763867972</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.654094164286774</v>
+        <v>-5.790363601454501</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7078628989288354</v>
+        <v>0.6533551240617448</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8479207641991487</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.59045842205284</v>
+        <v>-5.726727859220566</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7380119968767263</v>
+        <v>0.6835042220096357</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.7842850219652142</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.497458380846941</v>
+        <v>-5.633727818014668</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7564062721428813</v>
+        <v>0.7018984972757907</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.7842850219652142</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.257027884042081</v>
+        <v>-5.393297321209808</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8543215474897026</v>
+        <v>0.799813772622612</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.5438545251603539</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.184785315870887</v>
+        <v>-5.321054753038613</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8871478885930006</v>
+        <v>0.8326401137259101</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.5438545251603539</v>
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.105876217122001</v>
+        <v>-5.205114903413428</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9193901120098951</v>
+        <v>0.8796946374933241</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4817777259186707</v>
+        <v>-0.46703279414423</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.673030387621241</v>
+        <v>2.681877346685905</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.863220628698837</v>
+        <v>-4.962459314990264</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.013450418599154</v>
+        <v>0.9737549440825832</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4817777259186707</v>
+        <v>-0.46703279414423</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.670028458841234</v>
+        <v>2.678875417905898</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.643199830661827</v>
+        <v>-4.742438516953253</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.103037774824572</v>
+        <v>1.063342300308002</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3405578808506905</v>
+        <v>-0.3258129490762498</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.756339402892636</v>
+        <v>2.7651863619573</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.510332141598549</v>
+        <v>-4.609570827889976</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.172079033251707</v>
+        <v>1.132383558735136</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3405578808506905</v>
+        <v>-0.3258129490762498</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.77223358569446</v>
+        <v>2.781080544759124</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.350817038079179</v>
+        <v>-4.450055724370606</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.237030919099757</v>
+        <v>1.197335444583186</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1810427773313206</v>
+        <v>-0.1662978455568799</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.869088492246383</v>
+        <v>2.877935451311048</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.206144892979442</v>
+        <v>-4.305383579270869</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.304987879701091</v>
+        <v>1.265292405184521</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.03637063223158316</v>
+        <v>-0.02162570045714246</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.965979881867665</v>
+        <v>2.97482684093233</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.266019720337134</v>
+        <v>-4.365258406628561</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.26707544015944</v>
+        <v>1.227379965642869</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.09624545958927527</v>
+        <v>-0.08150052781483458</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.916092476854476</v>
+        <v>2.924939435919141</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.179220222558126</v>
+        <v>-4.278458908849553</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.32419573259361</v>
+        <v>1.284500258077039</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.09624545958927527</v>
+        <v>-0.08150052781483458</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.938492970177042</v>
+        <v>2.947339929241707</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.181689929019932</v>
+        <v>-4.280928615311359</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.323280251382299</v>
+        <v>1.283584776865729</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.09871516605108144</v>
+        <v>-0.08397023427664074</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.937083547673371</v>
+        <v>2.945930506738035</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.250060115343942</v>
+        <v>-4.349298801635369</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.306939099327397</v>
+        <v>1.267243624810827</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.08943946701486649</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.953655889569802</v>
+        <v>2.962502848634466</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.128643685717465</v>
+        <v>-4.227882372008892</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.345942379809879</v>
+        <v>1.306246905293309</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.08943946701486649</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.944092598201693</v>
+        <v>2.952939557266357</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.159636845046171</v>
+        <v>-4.258875531337598</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.158254681118784</v>
+        <v>1.118559206602213</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.08943946701486649</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.76880216324208</v>
+        <v>2.777649122306744</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.984162585253701</v>
+        <v>-4.083401271545128</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.233011617027559</v>
+        <v>1.193316142510989</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.08943946701486649</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.773369395233868</v>
+        <v>2.782216354298532</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.09509883789495</v>
+        <v>-4.098694056875608</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.164379144732267</v>
+        <v>1.162941057140004</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.08943946701486649</v>
+        <v>-0.0746945352404258</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.749111423995075</v>
+        <v>2.757958383059739</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77320672158129</v>
+        <v>3.773206721581288</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.298125415438183</v>
+        <v>-4.301720634418841</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.086299898934879</v>
+        <v>1.084861811342616</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2924660445580999</v>
+        <v>-0.2777211127836592</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.63042686268904</v>
+        <v>2.639273821753704</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734157</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.14019981650289</v>
+        <v>-4.143795035483548</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.159642524941129</v>
+        <v>1.158204437348866</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2924660445580999</v>
+        <v>-0.2777211127836592</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.640599249121172</v>
+        <v>2.649446208185837</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212293</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.053956353476512</v>
+        <v>-4.057551572457171</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.18908618072554</v>
+        <v>1.187648093133277</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2924660445580999</v>
+        <v>-0.2777211127836592</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.635545519695033</v>
+        <v>2.644392478759698</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786041</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.055139438127574</v>
+        <v>-4.058734657108232</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.180388722309641</v>
+        <v>1.178950634717378</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2981090930246114</v>
+        <v>-0.2833641612501707</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.623935466059652</v>
+        <v>2.632782425124316</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.932011731133491</v>
+        <v>-3.935606950114149</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.230191678140376</v>
+        <v>1.228753590548113</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2981090930246114</v>
+        <v>-0.2833641612501707</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.624487339092753</v>
+        <v>2.633334298157417</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.839201249682632</v>
+        <v>-3.84279646866329</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.196588562612085</v>
+        <v>1.195150475019822</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2052986115737521</v>
+        <v>-0.1905536797993114</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.609446319854634</v>
+        <v>2.618293278919299</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.790638197461601</v>
+        <v>-3.79423341644226</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.217887259425098</v>
+        <v>1.216449171832835</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1567355593527219</v>
+        <v>-0.1419906275782812</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.640457627111853</v>
+        <v>2.649304586176518</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.677966979225351</v>
+        <v>-3.681562198206009</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.258031455231321</v>
+        <v>1.256593367639058</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.04406434111647167</v>
+        <v>-0.02931940934203098</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.703136066565326</v>
+        <v>2.711983025629991</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.565589978042679</v>
+        <v>-3.569185197023337</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.308473551535058</v>
+        <v>1.307035463942794</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.04406434111647167</v>
+        <v>-0.02931940934203098</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.708627362395994</v>
+        <v>2.717474321460658</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.689594264968859</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.763824546929409</v>
+        <v>-3.767419765910067</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.240676925748905</v>
+        <v>1.239238838156641</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2422989100032023</v>
+        <v>-0.2275539782287616</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.601183822832494</v>
+        <v>2.610030781897159</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175319</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.846825827954688</v>
+        <v>-3.850421046935346</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.045832133339446</v>
+        <v>1.044394045747183</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.260869794530376</v>
+        <v>-0.2461248627559353</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.428397012116843</v>
+        <v>2.437243971181508</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.687631555898112</v>
+        <v>-3.69122677487877</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.229659502881282</v>
+        <v>1.228221415289019</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.260869794530376</v>
+        <v>-0.2461248627559353</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.548546672836049</v>
+        <v>2.557393631900713</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660767</v>
+        <v>3.733008865660765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.774230138879215</v>
+        <v>-3.777825357859873</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.209533095791164</v>
+        <v>1.208095008198901</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.260869794530376</v>
+        <v>-0.2461248627559353</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.563059698938372</v>
+        <v>2.571906658003036</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383421</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.735846476321063</v>
+        <v>-3.739441695301722</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.222306002156793</v>
+        <v>1.22086791456453</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2224861319722248</v>
+        <v>-0.2077412001977841</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.583509337815631</v>
+        <v>2.592356296880296</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.751143622002481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.558730146285897</v>
+        <v>-3.562325365266556</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.289881563016162</v>
+        <v>1.288443475423898</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2224861319722248</v>
+        <v>-0.2077412001977841</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.580238366660933</v>
+        <v>2.589085325725598</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263901</v>
+        <v>3.741324873263899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.529028022309604</v>
+        <v>-3.532623241290262</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.302445804368592</v>
+        <v>1.301007716776329</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2269562571875382</v>
+        <v>-0.2122113254130975</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.578239683293658</v>
+        <v>2.587086642358323</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481234</v>
+        <v>3.750725801481232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.349652601070836</v>
+        <v>-3.353247820051494</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.367982948170514</v>
+        <v>1.366544860578251</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.07017949901681952</v>
+        <v>-0.05543456724237883</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.666092713502504</v>
+        <v>2.674939672567168</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452229</v>
+        <v>3.716988143452227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.394666814591442</v>
+        <v>-3.3982620335721</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.330784718093861</v>
+        <v>1.329346630501598</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1005283943314241</v>
+        <v>-0.08578346255698344</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.628690831645331</v>
+        <v>2.637537790709995</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.737023032979534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.661671324863877</v>
+        <v>-3.665266543844536</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.229674476323833</v>
+        <v>1.228236388731569</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2948914323743727</v>
+        <v>-0.280146500599932</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.517764571158508</v>
+        <v>2.526611530223172</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230807</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.950458545322793</v>
+        <v>-3.954053764303451</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.113363510036768</v>
+        <v>1.111925422444505</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3959775524733731</v>
+        <v>-0.3812326206989324</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.456316820995609</v>
+        <v>2.465163780060273</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285453</v>
+        <v>3.705568086285451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.91798295915202</v>
+        <v>-3.921578178132679</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.123953706059394</v>
+        <v>1.12251561846713</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3959775524733731</v>
+        <v>-0.3812326206989324</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.453916782549925</v>
+        <v>2.46276374161459</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848101</v>
+        <v>3.709506867848099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.898944831444723</v>
+        <v>-3.902540050425381</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.128093676350558</v>
+        <v>1.126655588758294</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4541611638045676</v>
+        <v>-0.4394162320301269</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.415531334959454</v>
+        <v>2.424378294024118</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.73106089760125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.915690696701098</v>
+        <v>-3.919285915681757</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.298977199186688</v>
+        <v>1.297539111594425</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4541611638045676</v>
+        <v>-0.4394162320301269</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.593113203898134</v>
+        <v>2.601960162962799</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.96801107730189</v>
+        <v>-3.971606296282548</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.278882375932505</v>
+        <v>1.277444288340241</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4192143037956955</v>
+        <v>-0.4044693720212548</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.614914648889591</v>
+        <v>2.623761607954255</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259122</v>
+        <v>3.787422005259121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.112333983226809</v>
+        <v>-4.115929202207467</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.227161743959463</v>
+        <v>1.2257236563672</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4192143037956955</v>
+        <v>-0.4044693720212548</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.620923179286517</v>
+        <v>2.629770138351181</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989907</v>
+        <v>3.781497674989906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.964591012991807</v>
+        <v>-3.968186231972465</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.365411579845486</v>
+        <v>1.363973492253223</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2514069465608123</v>
+        <v>-0.2366620147863716</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.800760241419469</v>
+        <v>2.809607200484133</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224235365117</v>
+        <v>3.802242353651169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.066605695523028</v>
+        <v>-4.070200914503686</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.327399328364478</v>
+        <v>1.325961240772215</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2514069465608123</v>
+        <v>-0.2366620147863716</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.80355386295095</v>
+        <v>2.812400822015614</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.755531662824992</v>
+        <v>3.832279222689751</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.00026504071572</v>
+        <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.066605695523028</v>
+        <v>-4.169479936578231</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.327399328364478</v>
+        <v>1.286911980334056</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2514069465608123</v>
+        <v>-0.3359410368609164</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.993328837702088</v>
+        <v>2.753495757162546</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240518.xlsx
+++ b/tame_output/ON/bt/strategyON_20240518.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.1%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.5%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.2%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.8%</t>
+          <t>446.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-578.5%</t>
+          <t>-563.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-40.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.2%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-247.5%</t>
+          <t>-241.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-91.7%</t>
+          <t>-83.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-257.6%</t>
+          <t>-240.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-170.7%</t>
+          <t>-160.7%</t>
         </is>
       </c>
     </row>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.139039068395125</v>
+        <v>-8.090297183439249</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1425888727784126</v>
+        <v>-0.1230921187960621</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.435700410205323</v>
+        <v>-8.295092136730034</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2574744335732837</v>
+        <v>-0.2012311241831681</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.490102878384007</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.182554097141699</v>
+        <v>2.223100427792189</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.558944799420752</v>
+        <v>-8.418336525945463</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3107984937938584</v>
+        <v>-0.2545551844037428</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.490102878384007</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.178527792607296</v>
+        <v>2.219074123257786</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.941946188163383</v>
+        <v>-8.801337914688094</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4641011506124948</v>
+        <v>-0.4078578412223792</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.490102878384007</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.178425691285712</v>
+        <v>2.218972021936202</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.099345068376504</v>
+        <v>-8.958736794901215</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5244891867263131</v>
+        <v>-0.4682458773361975</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.647501758597129</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.08655787912927</v>
+        <v>2.127104209779759</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.458875390880506</v>
+        <v>-9.318267117405217</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6629510124298634</v>
+        <v>-0.6067077030397479</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.647501758597129</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.09190818242732</v>
+        <v>2.132454513077809</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.509224454334728</v>
+        <v>-9.368616180859439</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6751746178543749</v>
+        <v>-0.6189313084642594</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.765428039802166</v>
+        <v>-1.697850822051351</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.069614764311964</v>
+        <v>2.110161094962454</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.728373422408925</v>
+        <v>-9.587765148933636</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7597924544622852</v>
+        <v>-0.7035491450721696</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.984577007876364</v>
+        <v>-1.916999790125548</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.941167134089214</v>
+        <v>1.981713464739704</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.724682497452514</v>
+        <v>-9.584074223977225</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7583160844797208</v>
+        <v>-0.7020727750896052</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.984577007876364</v>
+        <v>-1.916999790125548</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.941167134089214</v>
+        <v>1.981713464739704</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.928940672782378</v>
+        <v>-9.788332399307089</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8345061574930237</v>
+        <v>-0.7782628481029081</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.112215952490353</v>
+        <v>-2.044638734739537</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.870096964439463</v>
+        <v>1.910643295089953</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.14697844441356</v>
+        <v>-10.00637017093827</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9172387116610587</v>
+        <v>-0.8609954022709432</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.286986720586252</v>
+        <v>-2.219409502835436</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.76971705806636</v>
+        <v>1.81026338871685</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.07350861274611</v>
+        <v>-9.932900339270818</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8724790775006577</v>
+        <v>-0.8162357681105425</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.213516888918803</v>
+        <v>-2.145939671167987</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.82917065856025</v>
+        <v>1.86971698921074</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.24863303013265</v>
+        <v>-10.10802475665736</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9279736237077589</v>
+        <v>-0.8717303143176434</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.388641306305347</v>
+        <v>-2.321064088554531</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.738651228875841</v>
+        <v>1.779197559526331</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.48308512414714</v>
+        <v>-10.34247685067185</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.02897362621515</v>
+        <v>-0.9727303168250345</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.388641306305347</v>
+        <v>-2.321064088554531</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.731432063974245</v>
+        <v>1.771978394624734</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.77088896868438</v>
+        <v>-10.63028069520909</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.150767354804022</v>
+        <v>-1.094524045413907</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.676445150842585</v>
+        <v>-2.608867933091769</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.552077566477926</v>
+        <v>1.592623897128415</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.8236751242847</v>
+        <v>-10.68306685080942</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.170766027205596</v>
+        <v>-1.114522717815481</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.772120637424982</v>
+        <v>-2.704543419674166</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.495788064367044</v>
+        <v>1.536334395017533</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.05570404402097</v>
+        <v>-10.91509577054568</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.260883866470987</v>
+        <v>-1.204640557080871</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.834133334613405</v>
+        <v>-2.766556116862589</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.461274174683105</v>
+        <v>1.501820505333594</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.00368853005215</v>
+        <v>-10.86308025657686</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.236087325197061</v>
+        <v>-1.179844015806945</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.834133334613405</v>
+        <v>-2.766556116862589</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.465264510369505</v>
+        <v>1.505810841019995</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.14536037177627</v>
+        <v>-11.00475209830098</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.294231288785451</v>
+        <v>-1.237987979395335</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.834133334613405</v>
+        <v>-2.766556116862589</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.463789283470764</v>
+        <v>1.504335614121253</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.09576952735144</v>
+        <v>-10.95516125387615</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.259341540850644</v>
+        <v>-1.203098231460528</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.784542490188572</v>
+        <v>-2.716965272437756</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.508597200290536</v>
+        <v>1.549143530941026</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.89661742011434</v>
+        <v>-10.75600914663905</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.192731831602488</v>
+        <v>-1.136488522212372</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.619219964238758</v>
+        <v>-2.551642746487942</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.594739582213741</v>
+        <v>1.635285912864231</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.67077226739493</v>
+        <v>-10.53016399391964</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.092814697478515</v>
+        <v>-1.036571388088399</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.577293288651595</v>
+        <v>-2.509716070900779</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.629474660602248</v>
+        <v>1.670020991252738</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.54619361105734</v>
+        <v>-10.40558533758205</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.041844090387419</v>
+        <v>-0.9856007809973026</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.577293288651595</v>
+        <v>-2.509716070900779</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.630613805158307</v>
+        <v>1.671160135808797</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.59908889910163</v>
+        <v>-10.45848062562633</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.060368431443027</v>
+        <v>-1.00412512205291</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.572337942563149</v>
+        <v>-2.504760724812332</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.636220786973482</v>
+        <v>1.676767117623972</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.31518016817288</v>
+        <v>-10.17457189469759</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.94107123483289</v>
+        <v>-0.8848279254427736</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.572337942563149</v>
+        <v>-2.504760724812332</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.641954491212119</v>
+        <v>1.682500821862609</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.24381377556323</v>
+        <v>-10.10320550208794</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9222619401828966</v>
+        <v>-0.8660186307927802</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.433394332202684</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.675037064384042</v>
+        <v>1.715583395034532</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.979976908359159</v>
+        <v>-9.839368634883868</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8266106746141761</v>
+        <v>-0.7703673652240597</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.433394332202684</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.665153583071135</v>
+        <v>1.705699913721625</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.712735107490762</v>
+        <v>-9.572126834015471</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7215485147661909</v>
+        <v>-0.6653052053760744</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.433394332202684</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.663319022571761</v>
+        <v>1.703865353222251</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.614828068814271</v>
+        <v>-9.47421979533898</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6826860142690552</v>
+        <v>-0.6264427048789392</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.432985800092944</v>
+        <v>-2.365408582342128</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.703810157514634</v>
+        <v>1.744356488165124</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.590874527838313</v>
+        <v>-9.450266254363022</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6724360917331786</v>
+        <v>-0.6161927823430622</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.409032259116987</v>
+        <v>-2.34145504136617</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.718850788245702</v>
+        <v>1.759397118896192</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.326814589515516</v>
+        <v>-9.186206316040225</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.580072432565812</v>
+        <v>-0.5238291231756955</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.144972320794191</v>
+        <v>-2.077395103043374</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.864026435077628</v>
+        <v>1.904572765728118</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.619734966010679</v>
+        <v>-8.479126692535388</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.300027616824178</v>
+        <v>-0.2437843074340615</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.144972320794191</v>
+        <v>-2.077395103043374</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.861239401417327</v>
+        <v>1.901785732067817</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.579550667644488</v>
+        <v>-8.438942394169198</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2836102735898605</v>
+        <v>-0.227366964199744</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.104788022428</v>
+        <v>-2.037210804677184</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.885693604324883</v>
+        <v>1.926239934975372</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.499480872106684</v>
+        <v>-8.358872598631393</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2522155341539816</v>
+        <v>-0.1959722247638656</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.024718226890196</v>
+        <v>-1.957141009139379</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.933102302868322</v>
+        <v>1.973648633518812</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.265999649877084</v>
+        <v>-8.125391376401794</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1508986164242896</v>
+        <v>-0.09465530703417313</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.791237004660597</v>
+        <v>-1.723659786909781</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.081115465043934</v>
+        <v>2.121661795694424</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.11633325886957</v>
+        <v>-7.975724985394279</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.09392427033424289</v>
+        <v>-0.03768096094412643</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.698333513418061</v>
+        <v>-1.630756295667245</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.133965349476496</v>
+        <v>2.174511680126986</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.984057785238684</v>
+        <v>-7.843449511763392</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.04564659413486138</v>
+        <v>0.01059671525525507</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.566058039787175</v>
+        <v>-1.498480822036358</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.208698120402055</v>
+        <v>2.249244451052545</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.793458110565531</v>
+        <v>-7.65284983709024</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.03340833642203656</v>
+        <v>0.08965164581215301</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.375458365114022</v>
+        <v>-1.307881147363205</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.325872985893583</v>
+        <v>2.366419316544073</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.54445831188195</v>
+        <v>-7.403850038406659</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1459145971191274</v>
+        <v>0.2021579065092443</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.375458365114022</v>
+        <v>-1.307881147363205</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.338779327117242</v>
+        <v>2.379325657767732</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.650048301655055</v>
+        <v>-7.509440028179763</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.02429732838933285</v>
+        <v>0.03194598100078361</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.481048354887126</v>
+        <v>-1.41347113713631</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.147449403654161</v>
+        <v>2.187995734304651</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.668783203773652</v>
+        <v>-7.52817493029836</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.01675305264031479</v>
+        <v>0.07299636203043125</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.481048354887126</v>
+        <v>-1.41347113713631</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.195993745531247</v>
+        <v>2.236540076181737</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.520843162366052</v>
+        <v>-7.380234888890761</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.04394985348481306</v>
+        <v>0.0122934559053034</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.460727438978569</v>
+        <v>-1.393150221227752</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.088307372388214</v>
+        <v>2.128853703038704</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.49661452597708</v>
+        <v>-7.356006252501788</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.04297238518270241</v>
+        <v>0.01327092420741405</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.36892158483878</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.094130567968119</v>
+        <v>2.134676898618609</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.453066119206389</v>
+        <v>-7.312457845731098</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.03251363456951939</v>
+        <v>0.02372967482059707</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.36892158483878</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.087169955873026</v>
+        <v>2.127716286523516</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.210917725752531</v>
+        <v>-7.07030945227724</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.07880807719316696</v>
+        <v>0.1350513865832834</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.36892158483878</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.101632310254169</v>
+        <v>2.142178640904659</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.147688353984183</v>
+        <v>-7.007080080508891</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.09863194635970141</v>
+        <v>0.1548752557498179</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.36892158483878</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.096164430713364</v>
+        <v>2.136710761363854</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.024397219167052</v>
+        <v>-6.88378894569176</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1454464942971305</v>
+        <v>0.201689803687247</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.313207667772466</v>
+        <v>-1.24563045002165</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.167637205614219</v>
+        <v>2.208183536264709</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.003248020263609</v>
+        <v>-6.862639746788317</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1616071520958329</v>
+        <v>0.2178504614859498</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.292058468869023</v>
+        <v>-1.224481251118206</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.188027703193611</v>
+        <v>2.2285740338441</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.759482578280164</v>
+        <v>-6.618874304804873</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2548940372362614</v>
+        <v>0.3111373466263783</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.292058468869023</v>
+        <v>-1.224481251118206</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.183808411540661</v>
+        <v>2.224354742191151</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.612585550562294</v>
+        <v>-6.471977277087003</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3157771622434256</v>
+        <v>0.372020471633542</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.176823009139618</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.21452767064783</v>
+        <v>2.25507400129832</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.362735156613219</v>
+        <v>-6.222126883137928</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4084593948067576</v>
+        <v>0.4647027041968741</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.176823009139618</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.207269745631532</v>
+        <v>2.247816076282022</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.186843064145787</v>
+        <v>-6.046234790670496</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4824153553143793</v>
+        <v>0.5386586647044957</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.176823009139618</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.210868869152181</v>
+        <v>2.251415199802671</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.015396601123324</v>
+        <v>-5.874788327648033</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5643214465779183</v>
+        <v>0.6205647559680347</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.072953763867972</v>
+        <v>-1.005376546117155</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.327064253020212</v>
+        <v>2.367610583670702</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.790363601454501</v>
+        <v>-5.64975532797921</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6533551240617448</v>
+        <v>0.7095984334518608</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8479207641991487</v>
+        <v>-0.7803435464483323</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.461104530437803</v>
+        <v>2.501650861088293</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.726727859220566</v>
+        <v>-5.586119585745275</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6835042220096357</v>
+        <v>0.7397475313997521</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7842850219652142</v>
+        <v>-0.7167078042143977</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.503980776832481</v>
+        <v>2.544527107482971</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.633727818014668</v>
+        <v>-5.493119544539377</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7018984972757907</v>
+        <v>0.7581418066659067</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7842850219652142</v>
+        <v>-0.7167078042143977</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.485175035616277</v>
+        <v>2.525721366266767</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.393297321209808</v>
+        <v>-5.252689047734517</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.799813772622612</v>
+        <v>0.8560570820127285</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5438545251603539</v>
+        <v>-0.4762773074095374</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.63117641032407</v>
+        <v>2.67172274097456</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.321054753038613</v>
+        <v>-5.180446479563322</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8326401137259101</v>
+        <v>0.8888834231160265</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5438545251603539</v>
+        <v>-0.4762773074095374</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.63510572415889</v>
+        <v>2.675652054809381</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.205114903413428</v>
+        <v>-5.064506629938137</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8796946374933241</v>
+        <v>0.9359379468834406</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.46703279414423</v>
+        <v>-0.3994555763934136</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.681877346685905</v>
+        <v>2.722423677336395</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.962459314990264</v>
+        <v>-4.951589792499289</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9737549440825832</v>
+        <v>0.9781027530789734</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.46703279414423</v>
+        <v>-0.3994555763934136</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.678875417905898</v>
+        <v>2.719421748556389</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.742438516953253</v>
+        <v>-4.731568994462278</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.063342300308002</v>
+        <v>1.067690109304392</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3258129490762498</v>
+        <v>-0.2582357313254333</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.7651863619573</v>
+        <v>2.805732692607791</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.609570827889976</v>
+        <v>-4.598701305399</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.132383558735136</v>
+        <v>1.136731367731526</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3258129490762498</v>
+        <v>-0.2582357313254333</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.781080544759124</v>
+        <v>2.821626875409614</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.450055724370606</v>
+        <v>-4.439186201879631</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.197335444583186</v>
+        <v>1.201683253579576</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1662978455568799</v>
+        <v>-0.09872062780606339</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.877935451311048</v>
+        <v>2.918481781961538</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.305383579270869</v>
+        <v>-4.294514056779893</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.265292405184521</v>
+        <v>1.269640214180911</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.02162570045714246</v>
+        <v>0.04595151729367403</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.97482684093233</v>
+        <v>3.01537317158282</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.365258406628561</v>
+        <v>-4.354388884137586</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.227379965642869</v>
+        <v>1.23172777463926</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.08150052781483458</v>
+        <v>-0.01392331006401809</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.924939435919141</v>
+        <v>2.965485766569631</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.278458908849553</v>
+        <v>-4.267589386358576</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.284500258077039</v>
+        <v>1.288848067073429</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.08150052781483458</v>
+        <v>-0.01392331006401809</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.947339929241707</v>
+        <v>2.987886259892197</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.280928615311359</v>
+        <v>-4.270059092820382</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.283584776865729</v>
+        <v>1.287932585862119</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.08397023427664074</v>
+        <v>-0.01639301652582426</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.945930506738035</v>
+        <v>2.986476837388525</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.349298801635369</v>
+        <v>-4.338429279144393</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.267243624810827</v>
+        <v>1.271591433807217</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.007117317489609309</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.962502848634466</v>
+        <v>3.003049179284956</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.227882372008892</v>
+        <v>-4.217012849517916</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.306246905293309</v>
+        <v>1.310594714289699</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.007117317489609309</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.952939557266357</v>
+        <v>2.993485887916847</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.258875531337598</v>
+        <v>-4.248006008846621</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.118559206602213</v>
+        <v>1.122907015598604</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.007117317489609309</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.777649122306744</v>
+        <v>2.818195452957234</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675897</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.083401271545128</v>
+        <v>-4.072531749054152</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.193316142510989</v>
+        <v>1.197663951507379</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.007117317489609309</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.782216354298532</v>
+        <v>2.822762684949022</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.765020747695442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.098694056875608</v>
+        <v>-4.183468001695401</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.162941057140004</v>
+        <v>1.129031479212087</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.0746945352404258</v>
+        <v>-0.007117317489609309</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.757958383059739</v>
+        <v>2.798504713710229</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581288</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.301720634418841</v>
+        <v>-4.386494579238634</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.084861811342616</v>
+        <v>1.050952233414699</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.2101438950328427</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.639273821753704</v>
+        <v>2.679820152404194</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734157</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.143795035483548</v>
+        <v>-4.228568980303341</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.158204437348866</v>
+        <v>1.124294859420949</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.2101438950328427</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.649446208185837</v>
+        <v>2.689992538836327</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212293</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.057551572457171</v>
+        <v>-4.142325517276963</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.187648093133277</v>
+        <v>1.15373851520536</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2777211127836592</v>
+        <v>-0.2101438950328427</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.644392478759698</v>
+        <v>2.684938809410187</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786041</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.058734657108232</v>
+        <v>-4.143508601928025</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.178950634717378</v>
+        <v>1.145041056789461</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2833641612501707</v>
+        <v>-0.2157869434993542</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.632782425124316</v>
+        <v>2.673328755774806</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.935606950114149</v>
+        <v>-4.020380894933941</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.228753590548113</v>
+        <v>1.194844012620196</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2833641612501707</v>
+        <v>-0.2157869434993542</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.633334298157417</v>
+        <v>2.673880628807908</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.84279646866329</v>
+        <v>-3.927570413483082</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.195150475019822</v>
+        <v>1.161240897091905</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1905536797993114</v>
+        <v>-0.1229764620484949</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.618293278919299</v>
+        <v>2.658839609569789</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.79423341644226</v>
+        <v>-3.879007361262052</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.216449171832835</v>
+        <v>1.182539593904918</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1419906275782812</v>
+        <v>-0.07441340982746469</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.649304586176518</v>
+        <v>2.689850916827007</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.681562198206009</v>
+        <v>-3.766336143025802</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.256593367639058</v>
+        <v>1.222683789711141</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.02931940934203098</v>
+        <v>0.03825780840878551</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.711983025629991</v>
+        <v>2.752529356280481</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.569185197023337</v>
+        <v>-3.653959141843129</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.307035463942794</v>
+        <v>1.273125886014877</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.02931940934203098</v>
+        <v>0.03825780840878551</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.717474321460658</v>
+        <v>2.758020652111148</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968859</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.767419765910067</v>
+        <v>-3.85219371072986</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.239238838156641</v>
+        <v>1.205329260228724</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2275539782287616</v>
+        <v>-0.1599767604779451</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.610030781897159</v>
+        <v>2.650577112547649</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175319</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.850421046935346</v>
+        <v>-3.935194991755139</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.044394045747183</v>
+        <v>1.010484467819266</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.1785476450051188</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.437243971181508</v>
+        <v>2.477790301831998</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199266</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.69122677487877</v>
+        <v>-3.776000719698562</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.228221415289019</v>
+        <v>1.194311837361102</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.1785476450051188</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.557393631900713</v>
+        <v>2.597939962551203</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660765</v>
+        <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.777825357859873</v>
+        <v>-3.862599302679665</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.208095008198901</v>
+        <v>1.174185430270984</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2461248627559353</v>
+        <v>-0.1785476450051188</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.571906658003036</v>
+        <v>2.612452988653526</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383421</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.739441695301722</v>
+        <v>-3.824215640121514</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.22086791456453</v>
+        <v>1.186958336636613</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2077412001977841</v>
+        <v>-0.1401639824469676</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.592356296880296</v>
+        <v>2.632902627530786</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002481</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.562325365266556</v>
+        <v>-3.647099310086348</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.288443475423898</v>
+        <v>1.254533897495981</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2077412001977841</v>
+        <v>-0.1401639824469676</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.589085325725598</v>
+        <v>2.629631656376088</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263899</v>
+        <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.532623241290262</v>
+        <v>-3.617397186110054</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.301007716776329</v>
+        <v>1.267098138848412</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2122113254130975</v>
+        <v>-0.144634107662281</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.587086642358323</v>
+        <v>2.627632973008813</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481232</v>
+        <v>3.750725801481234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.353247820051494</v>
+        <v>-3.438021764871286</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.366544860578251</v>
+        <v>1.332635282650334</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.05543456724237883</v>
+        <v>0.01214265050843766</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.674939672567168</v>
+        <v>2.715486003217658</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452227</v>
+        <v>3.716988143452229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.3982620335721</v>
+        <v>-3.483035978391892</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.329346630501598</v>
+        <v>1.295437052573681</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.08578346255698344</v>
+        <v>-0.01820624480616695</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.637537790709995</v>
+        <v>2.678084121360485</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979534</v>
+        <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.665266543844536</v>
+        <v>-3.750040488664328</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.228236388731569</v>
+        <v>1.194326810803652</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.280146500599932</v>
+        <v>-0.2125692828491155</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.526611530223172</v>
+        <v>2.567157860873662</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230807</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.954053764303451</v>
+        <v>-4.038827709123243</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.111925422444505</v>
+        <v>1.078015844516588</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.3136554029481159</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.465163780060273</v>
+        <v>2.505710110710763</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285451</v>
+        <v>3.705568086285453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.921578178132679</v>
+        <v>-4.006352122952471</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.12251561846713</v>
+        <v>1.088606040539213</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3812326206989324</v>
+        <v>-0.3136554029481159</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.46276374161459</v>
+        <v>2.50331007226508</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848099</v>
+        <v>3.709506867848101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.902540050425381</v>
+        <v>-3.987313995245174</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.126655588758294</v>
+        <v>1.092746010830377</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.3718390142793104</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.424378294024118</v>
+        <v>2.464924624674608</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.919285915681757</v>
+        <v>-4.004059860501549</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.297539111594425</v>
+        <v>1.263629533666508</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.4394162320301269</v>
+        <v>-0.3718390142793104</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.601960162962799</v>
+        <v>2.642506493613288</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537862</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.971606296282548</v>
+        <v>-4.056380241102341</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.277444288340241</v>
+        <v>1.243534710412324</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.3368921542704383</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.623761607954255</v>
+        <v>2.664307938604745</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259121</v>
+        <v>3.787422005259122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.115929202207467</v>
+        <v>-4.20070314702726</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.2257236563672</v>
+        <v>1.191814078439283</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4044693720212548</v>
+        <v>-0.3368921542704383</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.629770138351181</v>
+        <v>2.670316469001671</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989906</v>
+        <v>3.781497674989907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.968186231972465</v>
+        <v>-4.052960176792257</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.363973492253223</v>
+        <v>1.330063914325306</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.1690847970355551</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.809607200484133</v>
+        <v>2.850153531134623</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651169</v>
+        <v>3.80224235365117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.070200914503686</v>
+        <v>-4.154974859323478</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.325961240772215</v>
+        <v>1.292051662844298</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2366620147863716</v>
+        <v>-0.1690847970355551</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.812400822015614</v>
+        <v>2.852947152666104</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.832279222689751</v>
+        <v>3.515529936035889</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.169479936578231</v>
+        <v>-4.015448803790136</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.286911980334056</v>
+        <v>1.348524433449294</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.3359410368609164</v>
+        <v>-0.1690847970355551</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.753495757162546</v>
+        <v>2.853609501057762</v>
       </c>
     </row>
   </sheetData>
